--- a/regelwerk/Regelkatalog_24_KSVG_Entwurf.xlsx
+++ b/regelwerk/Regelkatalog_24_KSVG_Entwurf.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regeln" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regelregister" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schwellen nach Jahr" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Offene Punkte" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tätigkeitskatalog" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Abgabesätze" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pauschalen nach Jahr" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Textbausteine" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tätigkeitsabgrenzung" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Regeln" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Regelregister" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Schwellen nach Jahr" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Offene Punkte" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Tätigkeitskatalog" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Abgabesätze" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Pauschalen nach Jahr" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Textbausteine" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Tätigkeitsabgrenzung" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Regelregister'!$A$1:$J$23</definedName>
@@ -15138,7 +15138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" style="5" min="1" max="1"/>
@@ -16280,6 +16280,1196 @@
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>rechtsform.kein_entgelt</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ggmbh</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Rechtsform</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>R-138</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Ableitung: gGmbH ist eine GmbH</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>rechtsform.kein_entgelt</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>oeffentlich</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Rechtsform</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>F-006</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Oeffentliche Stelle ist kein selbststaendiger Kuenstler</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>sperre.summenabweichung</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>sperre</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Rechenprobe A2/A3: gedruckte Summe weicht von der Positionssumme ab</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>sperre.ust_inkonsistent</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>sperre</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Rechenprobe A2/A3: Umsatzsteuer ist nicht konsistent</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>sperre.positionsnummer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>sperre</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Rechenprobe A2/A3: Positionsnummer doppelt</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>sperre.rechnungsbetrag</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>sperre</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Rechenprobe A2/A3: Rechnungsbetrag ist nicht Netto plus Umsatzsteuer</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>sperre.negative_summe</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>sperre</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Rechenprobe A2/A3: negative Gesamtsumme</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>sperre.ust_satz</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>sperre</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Rechenprobe A2/A3: Umsatzsteuersatz ohne Hinweis</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>sperre.netto_fehlt</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>sperre</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Rechenprobe A2/A3: Nettosumme fehlt</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>sperre.doppelzahlung</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>sperre</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Rechenprobe A2/A3: Zahlung doppelt erfasst</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>auslage.nachgewiesen</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>auslage</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Art</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Paragraf 18 Abs. 1 Nr. 2 SGB IV: nachgewiesene Auslage</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>taetigkeit.synonym</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>gesang</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Quellenluecke: ohne Katalogtreffer keine automatische Entscheidung</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>taetigkeit.synonym</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>tanz</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Quellenluecke: ohne Katalogtreffer keine automatische Entscheidung</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>taetigkeit.synonym</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>choreografie</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Quellenluecke: ohne Katalogtreffer keine automatische Entscheidung</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>taetigkeit.synonym</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>regie</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Quellenluecke: ohne Katalogtreffer keine automatische Entscheidung</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>taetigkeit.synonym</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>komposition</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Quellenluecke: ohne Katalogtreffer keine automatische Entscheidung</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>taetigkeit.synonym</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>fotografie</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Quellenluecke: ohne Katalogtreffer keine automatische Entscheidung</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>taetigkeit.synonym</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>schauspiel</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Quellenluecke: ohne Katalogtreffer keine automatische Entscheidung</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>taetigkeit.synonym</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>dirigent</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Quellenluecke: ohne Katalogtreffer keine automatische Entscheidung</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>taetigkeit.synonym</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>bühnenbild</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Quellenluecke: ohne Katalogtreffer keine automatische Entscheidung</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>taetigkeit.synonym</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>straßenkünstler</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Quellenluecke: ohne Katalogtreffer keine automatische Entscheidung</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>taetigkeit.synonym</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>dj</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Quellenluecke: ohne Katalogtreffer keine automatische Entscheidung</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>taetigkeit.synonym</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>moderation</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Quellenluecke: ohne Katalogtreffer keine automatische Entscheidung</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>taetigkeit.synonym</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Quellenluecke: ohne Katalogtreffer keine automatische Entscheidung</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>taetigkeit.synonym</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>redaktion</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Quellenluecke: ohne Katalogtreffer keine automatische Entscheidung</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>taetigkeit.synonym</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>textbeitrag</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Quellenluecke: ohne Katalogtreffer keine automatische Entscheidung</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>taetigkeit.synonym</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>illustration</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Quellenluecke: ohne Katalogtreffer keine automatische Entscheidung</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>taetigkeit.synonym</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>podcast</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Quellenluecke: ohne Katalogtreffer keine automatische Entscheidung</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>taetigkeit.synonym</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>videojournalismus</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Quellenluecke: ohne Katalogtreffer keine automatische Entscheidung</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>taetigkeit.synonym</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>grafikdesign</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Quellenluecke: ohne Katalogtreffer keine automatische Entscheidung</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>taetigkeit.synonym</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>kameramann</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Quellenluecke: ohne Katalogtreffer keine automatische Entscheidung</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>taetigkeit.synonym</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>werbeflyer</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Quellenluecke: ohne Katalogtreffer keine automatische Entscheidung</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>taetigkeit.synonym</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>texterstellung</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Quellenluecke: ohne Katalogtreffer keine automatische Entscheidung</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>taetigkeit.synonym</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>eigenwerbung</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Quellenluecke: ohne Katalogtreffer keine automatische Entscheidung</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
@@ -24282,60 +25472,60 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t>T-76</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>Fotomodell, Model, Mannequin (Modellhonorar)</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="4" t="inlineStr">
         <is>
           <t>Grenzfall</t>
         </is>
       </c>
-      <c r="D47" t="n">
+      <c r="D47" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E47" s="4" t="inlineStr">
         <is>
           <t>fotomodell; modellhonorar; mannequin; dressman; laufstegmodel</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F47" s="4" t="inlineStr">
         <is>
           <t>Fotomodelle nennt KSK-Info 06 nicht; das Modell ordnete sie live als darstellende Kunst ein.</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="G47" s="4" t="inlineStr">
         <is>
           <t>R-137</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="H47" s="4" t="inlineStr">
         <is>
           <t>KSK-Info 06, Abschn. 1</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>Entwurf – vom Steuerberater zu prüfen</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
+      <c r="I47" s="4" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
         <is>
           <t>Neu 15.10.2026 (Alltagstest AT-2026-024, live f6a5d1a: Modellhonorar 800 € still mitgezählt, 382,20 € statt 343,00 €). Frage an den Steuerberater (Q-36).</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="K47" s="4" t="inlineStr">
         <is>
           <t>prüfen</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="M47" s="4" t="inlineStr">
         <is>
           <t>Abgrenzung offen.</t>
         </is>

--- a/regelwerk/Regelkatalog_24_KSVG_Entwurf.xlsx
+++ b/regelwerk/Regelkatalog_24_KSVG_Entwurf.xlsx
@@ -15138,7 +15138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J60"/>
+  <dimension ref="A1:J66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" style="5" min="1" max="1"/>
@@ -16286,1190 +16286,1400 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>rechtsform.kein_entgelt</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>ggmbh</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>Rechtsform</t>
         </is>
       </c>
-      <c r="E27" t="n">
+      <c r="E27" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H27" s="4" t="inlineStr">
         <is>
           <t>R-138</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="I27" s="4" t="inlineStr">
         <is>
           <t>Ableitung: gGmbH ist eine GmbH</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="J27" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>rechtsform.kein_entgelt</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>oeffentlich</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>Rechtsform</t>
         </is>
       </c>
-      <c r="E28" t="n">
+      <c r="E28" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H28" s="4" t="inlineStr">
         <is>
           <t>F-006</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="I28" s="4" t="inlineStr">
         <is>
           <t>Oeffentliche Stelle ist kein selbststaendiger Kuenstler</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="J28" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>sperre.summenabweichung</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>sperre</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E29" t="n">
+      <c r="E29" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H29" s="4" t="inlineStr">
         <is>
           <t>A2</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="I29" s="4" t="inlineStr">
         <is>
           <t>Rechenprobe A2/A3: gedruckte Summe weicht von der Positionssumme ab</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="J29" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>sperre.ust_inkonsistent</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>sperre</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E30" t="n">
+      <c r="E30" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H30" s="4" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="I30" s="4" t="inlineStr">
         <is>
           <t>Rechenprobe A2/A3: Umsatzsteuer ist nicht konsistent</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="J30" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>sperre.positionsnummer</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>sperre</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E31" t="n">
+      <c r="E31" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H31" s="4" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="I31" s="4" t="inlineStr">
         <is>
           <t>Rechenprobe A2/A3: Positionsnummer doppelt</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="J31" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>sperre.rechnungsbetrag</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>sperre</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E32" t="n">
+      <c r="E32" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="H32" s="4" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="I32" s="4" t="inlineStr">
         <is>
           <t>Rechenprobe A2/A3: Rechnungsbetrag ist nicht Netto plus Umsatzsteuer</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="J32" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>sperre.negative_summe</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>sperre</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E33" t="n">
+      <c r="E33" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="H33" s="4" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="I33" s="4" t="inlineStr">
         <is>
           <t>Rechenprobe A2/A3: negative Gesamtsumme</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="J33" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>sperre.ust_satz</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>sperre</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E34" t="n">
+      <c r="E34" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="H34" s="4" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="I34" s="4" t="inlineStr">
         <is>
           <t>Rechenprobe A2/A3: Umsatzsteuersatz ohne Hinweis</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="J34" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>sperre.netto_fehlt</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>sperre</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E35" t="n">
+      <c r="E35" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="H35" s="4" t="inlineStr">
         <is>
           <t>A2</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="I35" s="4" t="inlineStr">
         <is>
           <t>Rechenprobe A2/A3: Nettosumme fehlt</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="J35" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>sperre.doppelzahlung</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>sperre</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E36" t="n">
+      <c r="E36" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="H36" s="4" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="I36" s="4" t="inlineStr">
         <is>
           <t>Rechenprobe A2/A3: Zahlung doppelt erfasst</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="J36" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>auslage.nachgewiesen</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>auslage</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>Art</t>
         </is>
       </c>
-      <c r="E37" t="n">
+      <c r="E37" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="H37" s="4" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="I37" s="4" t="inlineStr">
         <is>
           <t>Paragraf 18 Abs. 1 Nr. 2 SGB IV: nachgewiesene Auslage</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="J37" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.synonym</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>gesang</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E38" t="n">
+      <c r="E38" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="H38" s="4" t="inlineStr">
         <is>
           <t>C4</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="I38" s="4" t="inlineStr">
         <is>
           <t>Quellenluecke: ohne Katalogtreffer keine automatische Entscheidung</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="J38" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.synonym</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>tanz</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E39" t="n">
+      <c r="E39" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="H39" s="4" t="inlineStr">
         <is>
           <t>C4</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="I39" s="4" t="inlineStr">
         <is>
           <t>Quellenluecke: ohne Katalogtreffer keine automatische Entscheidung</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="J39" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.synonym</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>choreografie</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E40" t="n">
+      <c r="E40" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="H40" s="4" t="inlineStr">
         <is>
           <t>C4</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="I40" s="4" t="inlineStr">
         <is>
           <t>Quellenluecke: ohne Katalogtreffer keine automatische Entscheidung</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="J40" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.synonym</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>regie</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E41" t="n">
+      <c r="E41" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="H41" s="4" t="inlineStr">
         <is>
           <t>C4</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="I41" s="4" t="inlineStr">
         <is>
           <t>Quellenluecke: ohne Katalogtreffer keine automatische Entscheidung</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="J41" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.synonym</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>komposition</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E42" t="n">
+      <c r="E42" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="H42" s="4" t="inlineStr">
         <is>
           <t>C4</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="I42" s="4" t="inlineStr">
         <is>
           <t>Quellenluecke: ohne Katalogtreffer keine automatische Entscheidung</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="J42" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.synonym</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>fotografie</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E43" t="n">
+      <c r="E43" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="H43" s="4" t="inlineStr">
         <is>
           <t>C4</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="I43" s="4" t="inlineStr">
         <is>
           <t>Quellenluecke: ohne Katalogtreffer keine automatische Entscheidung</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="J43" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.synonym</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t>schauspiel</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E44" t="n">
+      <c r="E44" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="H44" s="4" t="inlineStr">
         <is>
           <t>C4</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="I44" s="4" t="inlineStr">
         <is>
           <t>Quellenluecke: ohne Katalogtreffer keine automatische Entscheidung</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="J44" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.synonym</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>dirigent</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E45" t="n">
+      <c r="E45" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="H45" s="4" t="inlineStr">
         <is>
           <t>C4</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="I45" s="4" t="inlineStr">
         <is>
           <t>Quellenluecke: ohne Katalogtreffer keine automatische Entscheidung</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="J45" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.synonym</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="4" t="inlineStr">
         <is>
           <t>bühnenbild</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C46" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E46" t="n">
+      <c r="E46" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="H46" s="4" t="inlineStr">
         <is>
           <t>C4</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="I46" s="4" t="inlineStr">
         <is>
           <t>Quellenluecke: ohne Katalogtreffer keine automatische Entscheidung</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="J46" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.synonym</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>straßenkünstler</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E47" t="n">
+      <c r="E47" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="H47" s="4" t="inlineStr">
         <is>
           <t>C4</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="I47" s="4" t="inlineStr">
         <is>
           <t>Quellenluecke: ohne Katalogtreffer keine automatische Entscheidung</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="J47" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.synonym</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="4" t="inlineStr">
         <is>
           <t>dj</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C48" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E48" t="n">
+      <c r="E48" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="H48" s="4" t="inlineStr">
         <is>
           <t>C4</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="I48" s="4" t="inlineStr">
         <is>
           <t>Quellenluecke: ohne Katalogtreffer keine automatische Entscheidung</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="J48" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.synonym</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>moderation</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E49" t="n">
+      <c r="E49" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="H49" s="4" t="inlineStr">
         <is>
           <t>C4</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="I49" s="4" t="inlineStr">
         <is>
           <t>Quellenluecke: ohne Katalogtreffer keine automatische Entscheidung</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="J49" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.synonym</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t>feature</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C50" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E50" t="n">
+      <c r="E50" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="H50" s="4" t="inlineStr">
         <is>
           <t>C4</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="I50" s="4" t="inlineStr">
         <is>
           <t>Quellenluecke: ohne Katalogtreffer keine automatische Entscheidung</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="J50" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.synonym</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t>redaktion</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E51" t="n">
+      <c r="E51" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="H51" s="4" t="inlineStr">
         <is>
           <t>C4</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="I51" s="4" t="inlineStr">
         <is>
           <t>Quellenluecke: ohne Katalogtreffer keine automatische Entscheidung</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="J51" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.synonym</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="4" t="inlineStr">
         <is>
           <t>textbeitrag</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C52" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E52" t="n">
+      <c r="E52" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="H52" s="4" t="inlineStr">
         <is>
           <t>C4</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="I52" s="4" t="inlineStr">
         <is>
           <t>Quellenluecke: ohne Katalogtreffer keine automatische Entscheidung</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="J52" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.synonym</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="4" t="inlineStr">
         <is>
           <t>illustration</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C53" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E53" t="n">
+      <c r="E53" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="H53" s="4" t="inlineStr">
         <is>
           <t>C4</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="I53" s="4" t="inlineStr">
         <is>
           <t>Quellenluecke: ohne Katalogtreffer keine automatische Entscheidung</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="J53" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.synonym</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B54" s="4" t="inlineStr">
         <is>
           <t>podcast</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C54" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E54" t="n">
+      <c r="E54" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="H54" s="4" t="inlineStr">
         <is>
           <t>C4</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="I54" s="4" t="inlineStr">
         <is>
           <t>Quellenluecke: ohne Katalogtreffer keine automatische Entscheidung</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="J54" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="A55" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.synonym</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B55" s="4" t="inlineStr">
         <is>
           <t>videojournalismus</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C55" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E55" t="n">
+      <c r="E55" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="H55" s="4" t="inlineStr">
         <is>
           <t>C4</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="I55" s="4" t="inlineStr">
         <is>
           <t>Quellenluecke: ohne Katalogtreffer keine automatische Entscheidung</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="J55" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="A56" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.synonym</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B56" s="4" t="inlineStr">
         <is>
           <t>grafikdesign</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C56" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E56" t="n">
+      <c r="E56" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="H56" s="4" t="inlineStr">
         <is>
           <t>C4</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="I56" s="4" t="inlineStr">
         <is>
           <t>Quellenluecke: ohne Katalogtreffer keine automatische Entscheidung</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="J56" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="A57" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.synonym</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B57" s="4" t="inlineStr">
         <is>
           <t>kameramann</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C57" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E57" t="n">
+      <c r="E57" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="H57" s="4" t="inlineStr">
         <is>
           <t>C4</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="I57" s="4" t="inlineStr">
         <is>
           <t>Quellenluecke: ohne Katalogtreffer keine automatische Entscheidung</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="J57" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="A58" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.synonym</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B58" s="4" t="inlineStr">
         <is>
           <t>werbeflyer</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C58" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E58" t="n">
+      <c r="E58" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="H58" s="4" t="inlineStr">
         <is>
           <t>C4</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="I58" s="4" t="inlineStr">
         <is>
           <t>Quellenluecke: ohne Katalogtreffer keine automatische Entscheidung</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="J58" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
+      <c r="A59" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.synonym</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B59" s="4" t="inlineStr">
         <is>
           <t>texterstellung</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C59" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E59" t="n">
+      <c r="E59" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="H59" s="4" t="inlineStr">
         <is>
           <t>C4</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="I59" s="4" t="inlineStr">
         <is>
           <t>Quellenluecke: ohne Katalogtreffer keine automatische Entscheidung</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="J59" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="A60" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.synonym</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B60" s="4" t="inlineStr">
         <is>
           <t>eigenwerbung</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C60" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E60" t="n">
+      <c r="E60" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="H60" s="4" t="inlineStr">
         <is>
           <t>C4</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="I60" s="4" t="inlineStr">
         <is>
           <t>Quellenluecke: ohne Katalogtreffer keine automatische Entscheidung</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>sperre.manipulation</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>sperre</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Rechenprobe A2/A3: nachtraeglich geaenderte Zeile</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>sperre.paragraph19</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>sperre</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Rechenprobe A2/A3: Kleinunternehmer und Umsatzsteuer widersprechen sich</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>sperre.toleranz</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Euro</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Rechenprobe A2/A3: Rundungsdifferenz ueber 1 Cent</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>rechtsform.kein_entgelt</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>se</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Rechtsform</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>R-138</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Ableitung: die SE ist einer AG gleichgestellt</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>taetigkeit.ausgeschlossen</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>beratung</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>F-006</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Beratung ist keine kuenstlerische oder publizistische Leistung</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>taetigkeit.ausgeschlossen</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>buchhaltung</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>F-006</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Buchhaltung ist keine kuenstlerische oder publizistische Leistung</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>

--- a/regelwerk/Regelkatalog_24_KSVG_Entwurf.xlsx
+++ b/regelwerk/Regelkatalog_24_KSVG_Entwurf.xlsx
@@ -15138,7 +15138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J66"/>
+  <dimension ref="A1:J70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" style="5" min="1" max="1"/>
@@ -16433,7 +16433,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>sperre</t>
+          <t>doppelte Positionsnummer — Zeilensplitting oder Duplikat prüfen</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -16468,7 +16468,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>sperre</t>
+          <t>Rechenprobe brutto</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -16503,7 +16503,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>sperre</t>
+          <t>Negative Gesamtsumme ohne Stornorechnung</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -17476,210 +17476,350 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="A61" s="4" t="inlineStr">
         <is>
           <t>sperre.manipulation</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B61" s="4" t="inlineStr">
         <is>
           <t>sperre</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C61" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E61" t="n">
+      <c r="E61" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="H61" s="4" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="I61" s="4" t="inlineStr">
         <is>
           <t>Rechenprobe A2/A3: nachtraeglich geaenderte Zeile</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
+      <c r="J61" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="A62" s="4" t="inlineStr">
         <is>
           <t>sperre.paragraph19</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>sperre</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>Widerspruch §19 UStG — Rechnung prüfen</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E62" t="n">
+      <c r="E62" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="H62" s="4" t="inlineStr">
         <is>
           <t>A2</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="I62" s="4" t="inlineStr">
         <is>
           <t>Rechenprobe A2/A3: Kleinunternehmer und Umsatzsteuer widersprechen sich</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
+      <c r="J62" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="A63" s="4" t="inlineStr">
         <is>
           <t>sperre.toleranz</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B63" s="4" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C63" s="4" t="inlineStr">
         <is>
           <t>Euro</t>
         </is>
       </c>
-      <c r="E63" t="n">
+      <c r="E63" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="H63" s="4" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="I63" s="4" t="inlineStr">
         <is>
           <t>Rechenprobe A2/A3: Rundungsdifferenz ueber 1 Cent</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
+      <c r="J63" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="A64" s="4" t="inlineStr">
         <is>
           <t>rechtsform.kein_entgelt</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B64" s="4" t="inlineStr">
         <is>
           <t>se</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C64" s="4" t="inlineStr">
         <is>
           <t>Rechtsform</t>
         </is>
       </c>
-      <c r="E64" t="n">
+      <c r="E64" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="H64" s="4" t="inlineStr">
         <is>
           <t>R-138</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="I64" s="4" t="inlineStr">
         <is>
           <t>Ableitung: die SE ist einer AG gleichgestellt</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
+      <c r="J64" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
+      <c r="A65" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.ausgeschlossen</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B65" s="4" t="inlineStr">
         <is>
           <t>beratung</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C65" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E65" t="n">
+      <c r="E65" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="H65" s="4" t="inlineStr">
         <is>
           <t>F-006</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="I65" s="4" t="inlineStr">
         <is>
           <t>Beratung ist keine kuenstlerische oder publizistische Leistung</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
+      <c r="J65" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
+      <c r="A66" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.ausgeschlossen</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B66" s="4" t="inlineStr">
         <is>
           <t>buchhaltung</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C66" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E66" t="n">
+      <c r="E66" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="H66" s="4" t="inlineStr">
         <is>
           <t>F-006</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
+      <c r="I66" s="4" t="inlineStr">
         <is>
           <t>Buchhaltung ist keine kuenstlerische oder publizistische Leistung</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>sperre.toleranz_ab</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Euro</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Rechenprobe A2/A3: Rundungsdifferenz ab 2 Cent ist eine Sperre</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>sperre.toleranz_hinweis</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Rundungsdifferenz 1 ct, rechnerisch unbedeutend</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Rechenprobe A2/A3: bis 1 Cent kein Sperrgrund</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>offen.skonto</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Ist der Skonto in der Summe enthalten?</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Rechenprobe A2/A3: Skonto-Abzug unklar, keine Sperre</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>offen.storno</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Storno im selben Jahr: Saldierung ist zu prüfen</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Rechenprobe A2/A3: negative Summe mit Storno bleibt offen</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
@@ -23471,10 +23611,14 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>kompon; jingle; arrangeur; arrangement; musiker; sänger; audio-design; sounddesign; sound-design; discjockey; dj; liedermacher; songwriter; musik; konzert</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr"/>
+          <t>kompon; jingle; arrangeur; arrangement; musiker; sänger; audio-design; sounddesign; sound-design; discjockey; dj; liedermacher; songwriter; musik; konzert; konzertauftritt; konzerthonorar; konzertgage; konzertmitwirkung; live-konzert; musikdarbietung; musikauffuehrung</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>konzert und musik zaehlen nur, wenn sie die Leistung benennen. Blosse Erwaehnung (des Konzerts) ist kein Treffer.</t>
+        </is>
+      </c>
       <c r="G8" s="4" t="inlineStr"/>
       <c r="H8" s="4" t="inlineStr">
         <is>

--- a/regelwerk/Regelkatalog_24_KSVG_Entwurf.xlsx
+++ b/regelwerk/Regelkatalog_24_KSVG_Entwurf.xlsx
@@ -15138,7 +15138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J70"/>
+  <dimension ref="A1:J174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" style="5" min="1" max="1"/>
@@ -17686,140 +17686,3785 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
+      <c r="A67" s="4" t="inlineStr">
         <is>
           <t>sperre.toleranz_ab</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B67" s="4" t="inlineStr">
         <is>
           <t>0.02</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C67" s="4" t="inlineStr">
         <is>
           <t>Euro</t>
         </is>
       </c>
-      <c r="E67" t="n">
+      <c r="E67" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="H67" s="4" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
+      <c r="I67" s="4" t="inlineStr">
         <is>
           <t>Rechenprobe A2/A3: Rundungsdifferenz ab 2 Cent ist eine Sperre</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
+      <c r="J67" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
+      <c r="A68" s="4" t="inlineStr">
         <is>
           <t>sperre.toleranz_hinweis</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B68" s="4" t="inlineStr">
         <is>
           <t>Rundungsdifferenz 1 ct, rechnerisch unbedeutend</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C68" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E68" t="n">
+      <c r="E68" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="H68" s="4" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
+      <c r="I68" s="4" t="inlineStr">
         <is>
           <t>Rechenprobe A2/A3: bis 1 Cent kein Sperrgrund</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr">
+      <c r="J68" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
+      <c r="A69" s="4" t="inlineStr">
         <is>
           <t>offen.skonto</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B69" s="4" t="inlineStr">
         <is>
           <t>Ist der Skonto in der Summe enthalten?</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C69" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E69" t="n">
+      <c r="E69" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="H69" s="4" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
+      <c r="I69" s="4" t="inlineStr">
         <is>
           <t>Rechenprobe A2/A3: Skonto-Abzug unklar, keine Sperre</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr">
+      <c r="J69" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
+      <c r="A70" s="4" t="inlineStr">
         <is>
           <t>offen.storno</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B70" s="4" t="inlineStr">
         <is>
           <t>Storno im selben Jahr: Saldierung ist zu prüfen</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C70" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E70" t="n">
+      <c r="E70" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="H70" s="4" t="inlineStr">
         <is>
           <t>A4</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
+      <c r="I70" s="4" t="inlineStr">
         <is>
           <t>Rechenprobe A2/A3: negative Summe mit Storno bleibt offen</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr">
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>taetigkeit.synonym</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>clown</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Info-06</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>KSK-Info 06, Stand 09.2025, S. 2, Katalog künstlerische/publizistische Tätigkeiten: clown</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>taetigkeit.synonym</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>comedian</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Info-06</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>KSK-Info 06, Stand 09.2025, S. 2, Katalog künstlerische/publizistische Tätigkeiten: comedian</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>taetigkeit.synonym</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>kabarettist</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Info-06</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>KSK-Info 06, Stand 09.2025, S. 2, Katalog künstlerische/publizistische Tätigkeiten: kabarettist</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>taetigkeit.synonym</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>komiker</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Info-06</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>KSK-Info 06, Stand 09.2025, S. 2, Katalog künstlerische/publizistische Tätigkeiten: komiker</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>taetigkeit.synonym</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>illustrator</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Info-06</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>KSK-Info 06, Stand 09.2025, S. 2, Katalog künstlerische/publizistische Tätigkeiten: illustrator</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>taetigkeit.synonym</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>journalist</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Info-06</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>KSK-Info 06, Stand 09.2025, S. 2, Katalog künstlerische/publizistische Tätigkeiten: journalist</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>taetigkeit.synonym</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>kostümbildner</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Info-06</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>KSK-Info 06, Stand 09.2025, S. 2, Katalog künstlerische/publizistische Tätigkeiten: kostümbildner</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>taetigkeit.synonym</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>grafiker</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Info-06</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>KSK-Info 06, Stand 09.2025, S. 2, Katalog künstlerische/publizistische Tätigkeiten: grafiker</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>taetigkeit.synonym</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>bildhauer</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Info-06</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>KSK-Info 06, Stand 09.2025, S. 2, Katalog künstlerische/publizistische Tätigkeiten: bildhauer</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>taetigkeit.synonym</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>choreograph</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Info-06</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>KSK-Info 06, Stand 09.2025, S. 2, Katalog künstlerische/publizistische Tätigkeiten: choreograph</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>taetigkeit.synonym</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>fotograf</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Info-06</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>KSK-Info 06, Stand 09.2025, S. 2, Katalog künstlerische/publizistische Tätigkeiten: fotograf</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>taetigkeit.synonym</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>maler</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Info-06</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>KSK-Info 06, Stand 09.2025, S. 2, Katalog künstlerische/publizistische Tätigkeiten: maler</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>taetigkeit.synonym</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>maskenbilder</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Info-06</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>KSK-Info 06, Stand 09.2025, S. 2, Katalog künstlerische/publizistische Tätigkeiten: maskenbilder</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>taetigkeit.synonym</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>redakteur</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Info-06</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>KSK-Info 06, Stand 09.2025, S. 2, Katalog künstlerische/publizistische Tätigkeiten: redakteur</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>taetigkeit.synonym</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>musiker</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Info-06</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>KSK-Info 06, Stand 09.2025, S. 3, Katalog künstlerische/publizistische Tätigkeiten: musiker</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>taetigkeit.synonym</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>sänger</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Info-06</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>KSK-Info 06, Stand 09.2025, S. 3, Katalog künstlerische/publizistische Tätigkeiten: sänger</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>taetigkeit.synonym</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>schriftsteller</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Info-06</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>KSK-Info 06, Stand 09.2025, S. 3, Katalog künstlerische/publizistische Tätigkeiten: schriftsteller</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>taetigkeit.synonym</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>sprecher</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Info-06</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>KSK-Info 06, Stand 09.2025, S. 3, Katalog künstlerische/publizistische Tätigkeiten: sprecher</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>taetigkeit.synonym</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>synchronsprecher</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Info-06</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>KSK-Info 06, Stand 09.2025, S. 3, Katalog künstlerische/publizistische Tätigkeiten: synchronsprecher</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>taetigkeit.synonym</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>puppenspieler</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Info-06</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>KSK-Info 06, Stand 09.2025, S. 3, Katalog künstlerische/publizistische Tätigkeiten: puppenspieler</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>taetigkeit.synonym</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>marionettenspieler</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Info-06</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>KSK-Info 06, Stand 09.2025, S. 3, Katalog künstlerische/publizistische Tätigkeiten: marionettenspieler</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>taetigkeit.synonym</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>pantomime</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Info-06</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>KSK-Info 06, Stand 09.2025, S. 3, Katalog künstlerische/publizistische Tätigkeiten: pantomime</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>taetigkeit.synonym</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>zauberer</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Info-06</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>KSK-Info 06, Stand 09.2025, S. 3, Katalog künstlerische/publizistische Tätigkeiten: zauberer</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>taetigkeit.synonym</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>visagist</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Info-06</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>KSK-Info 06, Stand 09.2025, S. 3, Katalog künstlerische/publizistische Tätigkeiten: visagist</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>taetigkeit.synonym</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>instrumentalsolist</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Info-06</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>KSK-Info 06, Stand 09.2025, S. 3, Katalog künstlerische/publizistische Tätigkeiten: instrumentalsolist</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>taetigkeit.synonym</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>webdesigner</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Info-06</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>KSK-Info 06, Stand 09.2025, S. 3, Katalog künstlerische/publizistische Tätigkeiten: webdesigner</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>taetigkeit.synonym</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>web-designer</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Info-06</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>KSK-Info 06, Stand 09.2025, S. 3, Katalog künstlerische/publizistische Tätigkeiten: web-designer</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>taetigkeit.synonym</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>webdesign</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Info-06</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>KSK-Info 06, Stand 09.2025, S. 3, Katalog künstlerische/publizistische Tätigkeiten: webdesign</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>taetigkeit.synonym</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>maskenbildner</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Info-06</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>KSK-Info 06, Stand 09.2025, S. 3, Katalog künstlerische/publizistische Tätigkeiten: maskenbildner</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>taetigkeit.synonym</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>publizist</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Info-06</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>KSK-Info 06, Stand 09.2025, S. 3, Katalog künstlerische/publizistische Tätigkeiten: publizist</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>taetigkeit.synonym</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>reporter</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Info-06</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>KSK-Info 06, Stand 09.2025, S. 3, Katalog künstlerische/publizistische Tätigkeiten: reporter</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>taetigkeit.synonym</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>kritiker</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Info-06</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>KSK-Info 06, Stand 09.2025, S. 3, Katalog künstlerische/publizistische Tätigkeiten: kritiker</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>taetigkeit.synonym</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>herausgeber</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Info-06</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>KSK-Info 06, Stand 09.2025, S. 3, Katalog künstlerische/publizistische Tätigkeiten: herausgeber</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>taetigkeit.synonym</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>liedermacher</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Info-06</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>KSK-Info 06, Stand 09.2025, S. 3, Katalog künstlerische/publizistische Tätigkeiten: liedermacher</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>taetigkeit.synonym</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>songwriter</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Info-06</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>KSK-Info 06, Stand 09.2025, S. 3, Katalog künstlerische/publizistische Tätigkeiten: songwriter</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>taetigkeit.synonym</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>texter</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Info-06</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>KSK-Info 06, Stand 09.2025, S. 3, Katalog künstlerische/publizistische Tätigkeiten: texter</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>taetigkeit.synonym</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>layouter</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Info-06</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>KSK-Info 06, Stand 09.2025, S. 3, Katalog künstlerische/publizistische Tätigkeiten: layouter</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>taetigkeit.synonym</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>comiczeichner</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Info-06</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>KSK-Info 06, Stand 09.2025, S. 3, Katalog künstlerische/publizistische Tätigkeiten: comiczeichner</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>taetigkeit.synonym</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>karikaturist</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Info-06</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>KSK-Info 06, Stand 09.2025, S. 3, Katalog künstlerische/publizistische Tätigkeiten: karikaturist</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>taetigkeit.synonym</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>rezitator</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Info-06</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>KSK-Info 06, Stand 09.2025, S. 3, Katalog künstlerische/publizistische Tätigkeiten: rezitator</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>taetigkeit.synonym</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>drehbuchautor</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Info-06</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>KSK-Info 06, Stand 09.2025, S. 3, Katalog künstlerische/publizistische Tätigkeiten: drehbuchautor</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>taetigkeit.synonym</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>filmemacher</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Info-06</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>KSK-Info 06, Stand 09.2025, S. 3, Katalog künstlerische/publizistische Tätigkeiten: filmemacher</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>taetigkeit.synonym</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>regisseur</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Info-06</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>KSK-Info 06, Stand 09.2025, S. 3, Katalog künstlerische/publizistische Tätigkeiten: regisseur</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>taetigkeit.synonym</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>komponist</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Info-06</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>KSK-Info 06, Stand 09.2025, S. 3, Katalog künstlerische/publizistische Tätigkeiten: komponist</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>taetigkeit.synonym</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>autor</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Info-06</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>KSK-Info 06, Stand 09.2025, S. 3, Katalog künstlerische/publizistische Tätigkeiten: autor</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>taetigkeit.synonym</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>pressefotograf</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Info-06</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>KSK-Info 06, Stand 09.2025, S. 3, Katalog künstlerische/publizistische Tätigkeiten: pressefotograf</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>taetigkeit.synonym</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>werbefotograf</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Info-06</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>KSK-Info 06, Stand 09.2025, S. 3, Katalog künstlerische/publizistische Tätigkeiten: werbefotograf</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>taetigkeit.synonym</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>game-designer</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Info-06</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>KSK-Info 06, Stand 09.2025, S. 3, Katalog künstlerische/publizistische Tätigkeiten: game-designer</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>taetigkeit.synonym</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>corporate-design</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Info-02</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>KSK-Info 02, S. 1, Abschnitt 4: Corporate-Design ist eine Design-Leistung, die vom KSVG erfasst ist.</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>taetigkeit.offen</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>übersetzung</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Info-06-Offen</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>KSK-Info 06, S. 3: Übersetzer/Bearbeiter mit Fussnote * (Besonderheiten, schriftlich bei der KSK anfragen). Literarisch oder Fachübersetzung entscheidet der Einzelfall.</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>taetigkeit.offen</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>übersetzer</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Info-06-Offen</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>KSK-Info 06, S. 3: Übersetzer/Bearbeiter mit Fussnote *. Keine stille Wahl zwischen literarisch und Fachübersetzung.</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>taetigkeit.offen</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>übersetzerin</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Info-06-Offen</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>KSK-Info 06, S. 3: Übersetzer/Bearbeiter mit Fussnote *. Keine stille Wahl zwischen literarisch und Fachübersetzung.</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>taetigkeit.offen</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>uebersetzung</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Info-06-Offen</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>KSK-Info 06, S. 3: Übersetzer/Bearbeiter mit Fussnote *. Keine stille Wahl zwischen literarisch und Fachübersetzung.</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>taetigkeit.offen</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>uebersetzer</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Info-06-Offen</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>KSK-Info 06, S. 3: Übersetzer/Bearbeiter mit Fussnote *. Keine stille Wahl zwischen literarisch und Fachübersetzung.</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>taetigkeit.offen</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>kunstunterricht</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Info-06-Offen</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>KSK-Info 06, S. 1: Künstler ist auch, wer Kunst lehrt; S. 2 nennt Lehrer für künstlerische Tätigkeiten. Ob die konkrete Stunde nur Unterricht ist, sagt der Katalog nicht.</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>taetigkeit.offen</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>gesangsunterricht</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Info-06-Offen</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>KSK-Info 06, S. 3 nennt Musiklehrer, nicht die einzelne Gesangsstunde. Darbietung oder pädagogische Vermittlung bleibt Einzelfall.</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>taetigkeit.offen</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>stimmcoaching</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Info-06-Offen</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>KSK-Info 06 nennt Sprecherzieher und Musiklehrer, nicht Stimmcoaching. Pädagogische Vermittlung oder Darbietung ist nicht entschieden.</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>taetigkeit.offen</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>lektor</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Info-06-Offen</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>KSK-Info 06, S. 2 führt Lektor auf. Info 09, S. 4, Abschnitt 3.2: bei mehreren Leistungsanteilen entscheidet der überwiegende Teil. Kein Automatismus.</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>taetigkeit.offen</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>lektorat</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Info-06-Offen</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>KSK-Info 06, S. 2 führt Lektor auf. Info 09, S. 4, Abschnitt 3.2: bei mehreren Leistungsanteilen entscheidet der überwiegende Teil. Kein Automatismus.</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>ausland.kuenstler</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>ausländisch</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Info-22</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>KSK-Info 22, Stand 10.2025, S. 1-2, Abschn. 2 und 6: Abgabe auf selbständige ausländische Künstler ja, abhängige Beschäftigung und A1-Bescheinigung nein. Status nach deutschem Recht ist zu klären.</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>ausland.kuenstler</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>auslaendisch</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Info-22</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>KSK-Info 22, Stand 10.2025, S. 1-2, Abschn. 6: Die KSK prüft selbständige oder abhängige Tätigkeit nach deutschem Recht. Bescheinigungen des Auslands sind kein Nachweis.</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>ausland.kuenstler</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>auslandssachverhalt</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Info-22</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>KSK-Info 22, Stand 10.2025, S. 1 Abschn. 2: Auslandsbezug hebt die Abgabe nicht auf. Ob ein abhängiges Beschäftigungsverhältnis vorliegt, ist zu klären.</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>gemeinnuetzig</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>gemeinnützig</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Info-23</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>KSK-Info 23, Stand 01.2026, S. 1 Abschn. 2: Gemeinnützigkeit befreit nicht und begründet die Abgabe nicht allein. Befreiungstatbestände sind nicht vorgesehen.</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>gemeinnuetzig</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>gemeinnuetzig</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Info-23</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>KSK-Info 23, Stand 01.2026, S. 1 Abschn. 2: Gemeinnützigkeit befreit nicht und begründet die Abgabe nicht allein.</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>auftraggeber.kommune</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>stadt</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Info-11</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>KSK-Info 11, Stand der Datei, S. 1 Abschn. 1-2: Städte, Landkreise und Gemeinden können abgabepflichtig sein. Das ist kein Ausschluss wie eine Zahlung an eine öffentliche Körperschaft als Empfänger.</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>auftraggeber.kommune</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>landkreis</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Info-11</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>KSK-Info 11, Stand der Datei, S. 1 Abschn. 1-2: Städte, Landkreise und Gemeinden können abgabepflichtig sein. Das ist kein Ausschluss wie eine Zahlung an eine öffentliche Körperschaft als Empfänger.</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>auftraggeber.kommune</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>gemeinde</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Info-11</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>KSK-Info 11, Stand der Datei, S. 1 Abschn. 1-2: Städte, Landkreise und Gemeinden können abgabepflichtig sein. Das ist kein Ausschluss wie eine Zahlung an eine öffentliche Körperschaft als Empfänger.</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>gesellschafter.gmbh</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>gesellschafter</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Gesellschafter</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>KSK-Merkblatt Gesellschafter einer GmbH, S. 1-2: Mitarbeitender Gesellschafter ist nur bei maßgeblichem Einfluss selbständig. Künstlerischer Anteil und Oberleitung prüft die KSK. BSG 16.04.1998, B 3 KR 7/97 R, im Merkblatt zitiert.</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>musikverein.schueler_unter</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Schüler</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Info-12-P1</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>KSK-Info 12, Stand 01.2026, S. 2 Punkt 1: nicht mehr als 20 Schüler, dem Grunde nach keine Abgabepflicht nach § 24 Abs. 1 Nr. 9 KSVG.</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>musikverein.schueler_mitte</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>vermutung</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Info-12-P2</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>KSK-Info 12, Stand 01.2026, S. 2 Punkt 2: mehr als 20 und weniger als 61 Schüler, Vermutung keine Abgabepflicht nach § 24 Abs. 1 Nr. 9, wenn kein Ausbilder über der Übungsleiterpauschale liegt.</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>entgelt.ausgenommen</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>gema</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>KSVG-25</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>KSVG § 25 Abs. 2: Entgelte für Nutzungsrechte an Verwertungsgesellschaften sind ausgenommen (Gesetzestext im Repo, Seite 9).</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>entgelt.ausgenommen</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>verwertungsgesellschaft</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>KSVG-25</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>KSVG § 25 Abs. 2 Nr. 1: Entgelte an Verwertungsgesellschaften für urheberrechtliche Nutzungsrechte gehören nicht zum Entgelt.</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>entgelt.ausgenommen</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>verwertung</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>KSVG-25</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>KSVG § 25 Abs. 2 Nr. 1: Zahlung wegen Verwertung an eine Verwertungsgesellschaft, nicht schon jede Verlagsleistung.</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>entgelt.ausgenommen</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>musikverlag</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>KSVG-25</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>KSK-Checkliste Verlage und KSVG § 25 Abs. 2 Nr. 1: Lizenzzahlung, die als Verwertung ausgewiesen ist. Ein Verlag ist nicht schon deshalb eine Verwertungsgesellschaft.</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>auslage.mit_beleg_ausgenommen</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>reise</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>KSVEntgV-1</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>KSVEntgV § 1 Nr. 1: nachgewiesene Reisekosten innerhalb der Grenzen des § 3 Nr. 16 EStG zählen nicht. KSK-Info 10, S. 2.</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>auslage.mit_beleg_ausgenommen</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>fahrt</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>KSVEntgV-1</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>KSVEntgV § 1 Nr. 1: nachgewiesene Reisekosten innerhalb der Grenzen des § 3 Nr. 16 EStG zählen nicht. KSK-Info 10, S. 2.</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>auslage.mit_beleg_ausgenommen</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>KSVEntgV-1</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>KSVEntgV § 1 Nr. 1: nachgewiesene Reisekosten innerhalb der Grenzen des § 3 Nr. 16 EStG zählen nicht. KSK-Info 10, S. 2.</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>auslage.mit_beleg_ausgenommen</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>übernachtung</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>KSVEntgV-1</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>KSVEntgV § 1 Nr. 1: nachgewiesene Reisekosten innerhalb der Grenzen des § 3 Nr. 16 EStG zählen nicht. KSK-Info 10, S. 2.</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>auslage.mit_beleg_ausgenommen</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>uebernachtung</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>KSVEntgV-1</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>KSVEntgV § 1 Nr. 1: nachgewiesene Reisekosten innerhalb der Grenzen des § 3 Nr. 16 EStG zählen nicht. KSK-Info 10, S. 2.</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>auslage.mit_beleg_ausgenommen</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>verpflegung</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>KSVEntgV-1</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>KSVEntgV § 1 Nr. 1: nachgewiesene Reisekosten innerhalb der Grenzen des § 3 Nr. 16 EStG zählen nicht. KSK-Info 10, S. 2.</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>auslage.mit_beleg_ausgenommen</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>bewirtung</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>KSVEntgV-1</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>KSVEntgV § 1 und KSK-Info 10: nur die dort genannten nachgewiesenen Nebenleistungen fallen aus der Bemessung. Beleg erforderlich.</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>auslage.mit_beleg_ausgenommen</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>auslage</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>KSVEntgV-1</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>KSVEntgV § 1 und KSK-Info 10: nur die dort genannten nachgewiesenen Nebenleistungen fallen aus der Bemessung. Beleg erforderlich.</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>auslage.mit_beleg_ausgenommen</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>materialkosten</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>KSVEntgV-1</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>KSVEntgV § 1 und KSK-Info 10: nur die dort genannten nachgewiesenen Nebenleistungen fallen aus der Bemessung. Beleg erforderlich.</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>auslage.mit_beleg_ausgenommen</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>notenmappe</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>KSVEntgV-1</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>KSVEntgV § 1 und KSK-Info 10: nur die dort genannten nachgewiesenen Nebenleistungen fallen aus der Bemessung. Beleg erforderlich.</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>auslage.mit_beleg_ausgenommen</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>notenkauf</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>KSVEntgV-1</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>KSVEntgV § 1 und KSK-Info 10: nur die dort genannten nachgewiesenen Nebenleistungen fallen aus der Bemessung. Beleg erforderlich.</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>auslage.mit_beleg_ausgenommen</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>kostenübernahme</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>KSVEntgV-1</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>KSVEntgV § 1 und KSK-Info 10: nur die dort genannten nachgewiesenen Nebenleistungen fallen aus der Bemessung. Beleg erforderlich.</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>auslage.auch_ohne_beleg_ausgenommen</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>notenkauf</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>KSVEntgV-1</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Weiterberechnete Auslage Noten oder Kostenübernahme, wie bisher im Register auslage.nachgewiesen geführt.</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>auslage.auch_ohne_beleg_ausgenommen</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>kostenübernahme</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>KSVEntgV-1</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Weiterberechnete Auslage Noten oder Kostenübernahme, wie bisher im Register auslage.nachgewiesen geführt.</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>auslage.auch_ohne_beleg_ausgenommen</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>notenmappe</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>KSVEntgV-1</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Weiterberechnete Auslage Noten oder Kostenübernahme, wie bisher im Register auslage.nachgewiesen geführt.</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>auslage.ohne_beleg_offen</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>auslage</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>KSVEntgV-1</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>KSVEntgV § 1 Nr. 1 und Info 10: ohne Nachweis keine Ausnahme. Verpflegung zusätzlich an verpflegung.stunden_grenze und verpflegung.stunden_ganztag im Register gebunden.</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>auslage.ohne_beleg_offen</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>materialkosten</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>KSVEntgV-1</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>KSVEntgV § 1 Nr. 1 und Info 10: ohne Nachweis keine Ausnahme. Verpflegung zusätzlich an verpflegung.stunden_grenze und verpflegung.stunden_ganztag im Register gebunden.</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>auslage.ohne_beleg_offen</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>reise</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>KSVEntgV-1</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>KSVEntgV § 1 Nr. 1 und Info 10: ohne Nachweis keine Ausnahme. Verpflegung zusätzlich an verpflegung.stunden_grenze und verpflegung.stunden_ganztag im Register gebunden.</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>auslage.ohne_beleg_offen</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>fahrt</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>KSVEntgV-1</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>KSVEntgV § 1 Nr. 1 und Info 10: ohne Nachweis keine Ausnahme. Verpflegung zusätzlich an verpflegung.stunden_grenze und verpflegung.stunden_ganztag im Register gebunden.</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>auslage.ohne_beleg_offen</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>hotel</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>KSVEntgV-1</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>KSVEntgV § 1 Nr. 1 und Info 10: ohne Nachweis keine Ausnahme. Verpflegung zusätzlich an verpflegung.stunden_grenze und verpflegung.stunden_ganztag im Register gebunden.</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>auslage.ohne_beleg_offen</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>übernachtung</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>KSVEntgV-1</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>KSVEntgV § 1 Nr. 1 und Info 10: ohne Nachweis keine Ausnahme. Verpflegung zusätzlich an verpflegung.stunden_grenze und verpflegung.stunden_ganztag im Register gebunden.</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>auslage.ohne_beleg_offen</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>uebernachtung</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>KSVEntgV-1</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>KSVEntgV § 1 Nr. 1 und Info 10: ohne Nachweis keine Ausnahme. Verpflegung zusätzlich an verpflegung.stunden_grenze und verpflegung.stunden_ganztag im Register gebunden.</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>auslage.ohne_beleg_offen</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>verpflegung</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>KSVEntgV-1</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>KSVEntgV § 1 Nr. 1 und Info 10: ohne Nachweis keine Ausnahme. Verpflegung zusätzlich an verpflegung.stunden_grenze und verpflegung.stunden_ganztag im Register gebunden.</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>auslage.gehoert_zum_entgelt</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>porto</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Info-10</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>KSK-Info 10, S. 1: Auslagen und Nebenkosten, die dem Künstler vergütet werden, gehören zum Entgelt. Ausnahme nur Umsatzsteuer, Verwertungsgesellschaft, Reise und übliche Bewirtung.</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>auslage.gehoert_zum_entgelt</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>versand</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Info-10</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>KSK-Info 10, S. 1: Auslagen und Nebenkosten, die dem Künstler vergütet werden, gehören zum Entgelt. Ausnahme nur Umsatzsteuer, Verwertungsgesellschaft, Reise und übliche Bewirtung.</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>auslage.gehoert_zum_entgelt</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>kopierkosten</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Info-10</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>KSK-Info 10, S. 1: Auslagen und Nebenkosten, die dem Künstler vergütet werden, gehören zum Entgelt. Ausnahme nur Umsatzsteuer, Verwertungsgesellschaft, Reise und übliche Bewirtung.</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>auslage.gehoert_zum_entgelt</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>rahmen</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Info-10</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>KSK-Info 10, S. 1: Auslagen und Nebenkosten, die dem Künstler vergütet werden, gehören zum Entgelt. Ausnahme nur Umsatzsteuer, Verwertungsgesellschaft, Reise und übliche Bewirtung.</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>auslage.gehoert_zum_entgelt</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>plakat</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Info-10</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>KSK-Info 10, S. 1: Auslagen und Nebenkosten, die dem Künstler vergütet werden, gehören zum Entgelt. Ausnahme nur Umsatzsteuer, Verwertungsgesellschaft, Reise und übliche Bewirtung.</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>auslage.gehoert_zum_entgelt</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>scanner-miete</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E173" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Info-10</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>KSK-Info 10, S. 1: Auslagen und Nebenkosten, die dem Künstler vergütet werden, gehören zum Entgelt. Ausnahme nur Umsatzsteuer, Verwertungsgesellschaft, Reise und übliche Bewirtung.</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>auslage.gehoert_zum_entgelt</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>notenmaterial</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E174" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Info-10</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>KSK-Info 10, S. 1: Auslagen und Nebenkosten, die dem Künstler vergütet werden, gehören zum Entgelt. Ausnahme nur Umsatzsteuer, Verwertungsgesellschaft, Reise und übliche Bewirtung.</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>

--- a/regelwerk/Regelkatalog_24_KSVG_Entwurf.xlsx
+++ b/regelwerk/Regelkatalog_24_KSVG_Entwurf.xlsx
@@ -15138,7 +15138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J174"/>
+  <dimension ref="A1:J177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" style="5" min="1" max="1"/>
@@ -17443,7 +17443,7 @@
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>taetigkeit.synonym</t>
+          <t>szenarien.eigenwerbung</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
@@ -17461,12 +17461,12 @@
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>KSVG-24-2</t>
         </is>
       </c>
       <c r="I60" s="4" t="inlineStr">
         <is>
-          <t>Quellenluecke: ohne Katalogtreffer keine automatische Entscheidung</t>
+          <t>KSVG § 24 Abs. 2 Satz 1 Nummer 1. Eigenwerbung ist ein Verwerter-Szenario, keine Tätigkeit.</t>
         </is>
       </c>
       <c r="J60" s="4" t="inlineStr">
@@ -17826,3645 +17826,3750 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
+      <c r="A71" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.synonym</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B71" s="4" t="inlineStr">
         <is>
           <t>clown</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="C71" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E71" t="n">
+      <c r="E71" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="H71" s="4" t="inlineStr">
         <is>
           <t>Info-06</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
+      <c r="I71" s="4" t="inlineStr">
         <is>
           <t>KSK-Info 06, Stand 09.2025, S. 2, Katalog künstlerische/publizistische Tätigkeiten: clown</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr">
+      <c r="J71" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
+      <c r="A72" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.synonym</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B72" s="4" t="inlineStr">
         <is>
           <t>comedian</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C72" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E72" t="n">
+      <c r="E72" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="H72" s="4" t="inlineStr">
         <is>
           <t>Info-06</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
+      <c r="I72" s="4" t="inlineStr">
         <is>
           <t>KSK-Info 06, Stand 09.2025, S. 2, Katalog künstlerische/publizistische Tätigkeiten: comedian</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr">
+      <c r="J72" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
+      <c r="A73" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.synonym</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B73" s="4" t="inlineStr">
         <is>
           <t>kabarettist</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="C73" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E73" t="n">
+      <c r="E73" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="H73" s="4" t="inlineStr">
         <is>
           <t>Info-06</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
+      <c r="I73" s="4" t="inlineStr">
         <is>
           <t>KSK-Info 06, Stand 09.2025, S. 2, Katalog künstlerische/publizistische Tätigkeiten: kabarettist</t>
         </is>
       </c>
-      <c r="J73" t="inlineStr">
+      <c r="J73" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
+      <c r="A74" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.synonym</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B74" s="4" t="inlineStr">
         <is>
           <t>komiker</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C74" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E74" t="n">
+      <c r="E74" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="H74" s="4" t="inlineStr">
         <is>
           <t>Info-06</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
+      <c r="I74" s="4" t="inlineStr">
         <is>
           <t>KSK-Info 06, Stand 09.2025, S. 2, Katalog künstlerische/publizistische Tätigkeiten: komiker</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr">
+      <c r="J74" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
+      <c r="A75" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.synonym</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B75" s="4" t="inlineStr">
         <is>
           <t>illustrator</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C75" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E75" t="n">
+      <c r="E75" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="H75" s="4" t="inlineStr">
         <is>
           <t>Info-06</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
+      <c r="I75" s="4" t="inlineStr">
         <is>
           <t>KSK-Info 06, Stand 09.2025, S. 2, Katalog künstlerische/publizistische Tätigkeiten: illustrator</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr">
+      <c r="J75" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
+      <c r="A76" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.synonym</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B76" s="4" t="inlineStr">
         <is>
           <t>journalist</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C76" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E76" t="n">
+      <c r="E76" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="H76" s="4" t="inlineStr">
         <is>
           <t>Info-06</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
+      <c r="I76" s="4" t="inlineStr">
         <is>
           <t>KSK-Info 06, Stand 09.2025, S. 2, Katalog künstlerische/publizistische Tätigkeiten: journalist</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr">
+      <c r="J76" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
+      <c r="A77" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.synonym</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B77" s="4" t="inlineStr">
         <is>
           <t>kostümbildner</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C77" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E77" t="n">
+      <c r="E77" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="H77" s="4" t="inlineStr">
         <is>
           <t>Info-06</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
+      <c r="I77" s="4" t="inlineStr">
         <is>
           <t>KSK-Info 06, Stand 09.2025, S. 2, Katalog künstlerische/publizistische Tätigkeiten: kostümbildner</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr">
+      <c r="J77" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
+      <c r="A78" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.synonym</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B78" s="4" t="inlineStr">
         <is>
           <t>grafiker</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="C78" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E78" t="n">
+      <c r="E78" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="H78" s="4" t="inlineStr">
         <is>
           <t>Info-06</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
+      <c r="I78" s="4" t="inlineStr">
         <is>
           <t>KSK-Info 06, Stand 09.2025, S. 2, Katalog künstlerische/publizistische Tätigkeiten: grafiker</t>
         </is>
       </c>
-      <c r="J78" t="inlineStr">
+      <c r="J78" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
+      <c r="A79" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.synonym</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B79" s="4" t="inlineStr">
         <is>
           <t>bildhauer</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C79" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E79" t="n">
+      <c r="E79" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="H79" s="4" t="inlineStr">
         <is>
           <t>Info-06</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
+      <c r="I79" s="4" t="inlineStr">
         <is>
           <t>KSK-Info 06, Stand 09.2025, S. 2, Katalog künstlerische/publizistische Tätigkeiten: bildhauer</t>
         </is>
       </c>
-      <c r="J79" t="inlineStr">
+      <c r="J79" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
+      <c r="A80" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.synonym</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B80" s="4" t="inlineStr">
         <is>
           <t>choreograph</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="C80" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E80" t="n">
+      <c r="E80" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="H80" s="4" t="inlineStr">
         <is>
           <t>Info-06</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
+      <c r="I80" s="4" t="inlineStr">
         <is>
           <t>KSK-Info 06, Stand 09.2025, S. 2, Katalog künstlerische/publizistische Tätigkeiten: choreograph</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr">
+      <c r="J80" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
+      <c r="A81" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.synonym</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B81" s="4" t="inlineStr">
         <is>
           <t>fotograf</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="C81" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E81" t="n">
+      <c r="E81" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="H81" s="4" t="inlineStr">
         <is>
           <t>Info-06</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
+      <c r="I81" s="4" t="inlineStr">
         <is>
           <t>KSK-Info 06, Stand 09.2025, S. 2, Katalog künstlerische/publizistische Tätigkeiten: fotograf</t>
         </is>
       </c>
-      <c r="J81" t="inlineStr">
+      <c r="J81" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
+      <c r="A82" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.synonym</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B82" s="4" t="inlineStr">
         <is>
           <t>maler</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="C82" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E82" t="n">
+      <c r="E82" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H82" t="inlineStr">
+      <c r="H82" s="4" t="inlineStr">
         <is>
           <t>Info-06</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
+      <c r="I82" s="4" t="inlineStr">
         <is>
           <t>KSK-Info 06, Stand 09.2025, S. 2, Katalog künstlerische/publizistische Tätigkeiten: maler</t>
         </is>
       </c>
-      <c r="J82" t="inlineStr">
+      <c r="J82" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
+      <c r="A83" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.synonym</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B83" s="4" t="inlineStr">
         <is>
           <t>maskenbilder</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="C83" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E83" t="n">
+      <c r="E83" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H83" t="inlineStr">
+      <c r="H83" s="4" t="inlineStr">
         <is>
           <t>Info-06</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
+      <c r="I83" s="4" t="inlineStr">
         <is>
           <t>KSK-Info 06, Stand 09.2025, S. 2, Katalog künstlerische/publizistische Tätigkeiten: maskenbilder</t>
         </is>
       </c>
-      <c r="J83" t="inlineStr">
+      <c r="J83" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
+      <c r="A84" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.synonym</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="B84" s="4" t="inlineStr">
         <is>
           <t>redakteur</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
+      <c r="C84" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E84" t="n">
+      <c r="E84" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H84" t="inlineStr">
+      <c r="H84" s="4" t="inlineStr">
         <is>
           <t>Info-06</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
+      <c r="I84" s="4" t="inlineStr">
         <is>
           <t>KSK-Info 06, Stand 09.2025, S. 2, Katalog künstlerische/publizistische Tätigkeiten: redakteur</t>
         </is>
       </c>
-      <c r="J84" t="inlineStr">
+      <c r="J84" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
+      <c r="A85" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.synonym</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B85" s="4" t="inlineStr">
         <is>
           <t>musiker</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="C85" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E85" t="n">
+      <c r="E85" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H85" t="inlineStr">
+      <c r="H85" s="4" t="inlineStr">
         <is>
           <t>Info-06</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
+      <c r="I85" s="4" t="inlineStr">
         <is>
           <t>KSK-Info 06, Stand 09.2025, S. 3, Katalog künstlerische/publizistische Tätigkeiten: musiker</t>
         </is>
       </c>
-      <c r="J85" t="inlineStr">
+      <c r="J85" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
+      <c r="A86" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.synonym</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B86" s="4" t="inlineStr">
         <is>
           <t>sänger</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
+      <c r="C86" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E86" t="n">
+      <c r="E86" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H86" t="inlineStr">
+      <c r="H86" s="4" t="inlineStr">
         <is>
           <t>Info-06</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
+      <c r="I86" s="4" t="inlineStr">
         <is>
           <t>KSK-Info 06, Stand 09.2025, S. 3, Katalog künstlerische/publizistische Tätigkeiten: sänger</t>
         </is>
       </c>
-      <c r="J86" t="inlineStr">
+      <c r="J86" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
+      <c r="A87" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.synonym</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B87" s="4" t="inlineStr">
         <is>
           <t>schriftsteller</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="C87" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E87" t="n">
+      <c r="E87" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H87" t="inlineStr">
+      <c r="H87" s="4" t="inlineStr">
         <is>
           <t>Info-06</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
+      <c r="I87" s="4" t="inlineStr">
         <is>
           <t>KSK-Info 06, Stand 09.2025, S. 3, Katalog künstlerische/publizistische Tätigkeiten: schriftsteller</t>
         </is>
       </c>
-      <c r="J87" t="inlineStr">
+      <c r="J87" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
+      <c r="A88" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.synonym</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B88" s="4" t="inlineStr">
         <is>
           <t>sprecher</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="C88" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E88" t="n">
+      <c r="E88" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H88" t="inlineStr">
+      <c r="H88" s="4" t="inlineStr">
         <is>
           <t>Info-06</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr">
+      <c r="I88" s="4" t="inlineStr">
         <is>
           <t>KSK-Info 06, Stand 09.2025, S. 3, Katalog künstlerische/publizistische Tätigkeiten: sprecher</t>
         </is>
       </c>
-      <c r="J88" t="inlineStr">
+      <c r="J88" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
+      <c r="A89" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.synonym</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="B89" s="4" t="inlineStr">
         <is>
           <t>synchronsprecher</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
+      <c r="C89" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E89" t="n">
+      <c r="E89" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H89" t="inlineStr">
+      <c r="H89" s="4" t="inlineStr">
         <is>
           <t>Info-06</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
+      <c r="I89" s="4" t="inlineStr">
         <is>
           <t>KSK-Info 06, Stand 09.2025, S. 3, Katalog künstlerische/publizistische Tätigkeiten: synchronsprecher</t>
         </is>
       </c>
-      <c r="J89" t="inlineStr">
+      <c r="J89" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
+      <c r="A90" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.synonym</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="B90" s="4" t="inlineStr">
         <is>
           <t>puppenspieler</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
+      <c r="C90" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E90" t="n">
+      <c r="E90" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H90" t="inlineStr">
+      <c r="H90" s="4" t="inlineStr">
         <is>
           <t>Info-06</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
+      <c r="I90" s="4" t="inlineStr">
         <is>
           <t>KSK-Info 06, Stand 09.2025, S. 3, Katalog künstlerische/publizistische Tätigkeiten: puppenspieler</t>
         </is>
       </c>
-      <c r="J90" t="inlineStr">
+      <c r="J90" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
+      <c r="A91" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.synonym</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="B91" s="4" t="inlineStr">
         <is>
           <t>marionettenspieler</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
+      <c r="C91" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E91" t="n">
+      <c r="E91" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H91" t="inlineStr">
+      <c r="H91" s="4" t="inlineStr">
         <is>
           <t>Info-06</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr">
+      <c r="I91" s="4" t="inlineStr">
         <is>
           <t>KSK-Info 06, Stand 09.2025, S. 3, Katalog künstlerische/publizistische Tätigkeiten: marionettenspieler</t>
         </is>
       </c>
-      <c r="J91" t="inlineStr">
+      <c r="J91" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
+      <c r="A92" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.synonym</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="B92" s="4" t="inlineStr">
         <is>
           <t>pantomime</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
+      <c r="C92" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E92" t="n">
+      <c r="E92" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H92" t="inlineStr">
+      <c r="H92" s="4" t="inlineStr">
         <is>
           <t>Info-06</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr">
+      <c r="I92" s="4" t="inlineStr">
         <is>
           <t>KSK-Info 06, Stand 09.2025, S. 3, Katalog künstlerische/publizistische Tätigkeiten: pantomime</t>
         </is>
       </c>
-      <c r="J92" t="inlineStr">
+      <c r="J92" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
+      <c r="A93" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.synonym</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="B93" s="4" t="inlineStr">
         <is>
           <t>zauberer</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="C93" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E93" t="n">
+      <c r="E93" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H93" t="inlineStr">
+      <c r="H93" s="4" t="inlineStr">
         <is>
           <t>Info-06</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr">
+      <c r="I93" s="4" t="inlineStr">
         <is>
           <t>KSK-Info 06, Stand 09.2025, S. 3, Katalog künstlerische/publizistische Tätigkeiten: zauberer</t>
         </is>
       </c>
-      <c r="J93" t="inlineStr">
+      <c r="J93" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
+      <c r="A94" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.synonym</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
+      <c r="B94" s="4" t="inlineStr">
         <is>
           <t>visagist</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
+      <c r="C94" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E94" t="n">
+      <c r="E94" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H94" t="inlineStr">
+      <c r="H94" s="4" t="inlineStr">
         <is>
           <t>Info-06</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr">
+      <c r="I94" s="4" t="inlineStr">
         <is>
           <t>KSK-Info 06, Stand 09.2025, S. 3, Katalog künstlerische/publizistische Tätigkeiten: visagist</t>
         </is>
       </c>
-      <c r="J94" t="inlineStr">
+      <c r="J94" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
+      <c r="A95" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.synonym</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="B95" s="4" t="inlineStr">
         <is>
           <t>instrumentalsolist</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
+      <c r="C95" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E95" t="n">
+      <c r="E95" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H95" t="inlineStr">
+      <c r="H95" s="4" t="inlineStr">
         <is>
           <t>Info-06</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr">
+      <c r="I95" s="4" t="inlineStr">
         <is>
           <t>KSK-Info 06, Stand 09.2025, S. 3, Katalog künstlerische/publizistische Tätigkeiten: instrumentalsolist</t>
         </is>
       </c>
-      <c r="J95" t="inlineStr">
+      <c r="J95" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
+      <c r="A96" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.synonym</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
+      <c r="B96" s="4" t="inlineStr">
         <is>
           <t>webdesigner</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
+      <c r="C96" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E96" t="n">
+      <c r="E96" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H96" t="inlineStr">
+      <c r="H96" s="4" t="inlineStr">
         <is>
           <t>Info-06</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr">
+      <c r="I96" s="4" t="inlineStr">
         <is>
           <t>KSK-Info 06, Stand 09.2025, S. 3, Katalog künstlerische/publizistische Tätigkeiten: webdesigner</t>
         </is>
       </c>
-      <c r="J96" t="inlineStr">
+      <c r="J96" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
+      <c r="A97" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.synonym</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
+      <c r="B97" s="4" t="inlineStr">
         <is>
           <t>web-designer</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
+      <c r="C97" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E97" t="n">
+      <c r="E97" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H97" t="inlineStr">
+      <c r="H97" s="4" t="inlineStr">
         <is>
           <t>Info-06</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr">
+      <c r="I97" s="4" t="inlineStr">
         <is>
           <t>KSK-Info 06, Stand 09.2025, S. 3, Katalog künstlerische/publizistische Tätigkeiten: web-designer</t>
         </is>
       </c>
-      <c r="J97" t="inlineStr">
+      <c r="J97" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.synonym</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
+      <c r="B98" s="4" t="inlineStr">
         <is>
           <t>webdesign</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
+      <c r="C98" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E98" t="n">
+      <c r="E98" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H98" t="inlineStr">
+      <c r="H98" s="4" t="inlineStr">
         <is>
           <t>Info-06</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr">
+      <c r="I98" s="4" t="inlineStr">
         <is>
           <t>KSK-Info 06, Stand 09.2025, S. 3, Katalog künstlerische/publizistische Tätigkeiten: webdesign</t>
         </is>
       </c>
-      <c r="J98" t="inlineStr">
+      <c r="J98" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
+      <c r="A99" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.synonym</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
+      <c r="B99" s="4" t="inlineStr">
         <is>
           <t>maskenbildner</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
+      <c r="C99" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E99" t="n">
+      <c r="E99" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H99" t="inlineStr">
+      <c r="H99" s="4" t="inlineStr">
         <is>
           <t>Info-06</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr">
+      <c r="I99" s="4" t="inlineStr">
         <is>
           <t>KSK-Info 06, Stand 09.2025, S. 3, Katalog künstlerische/publizistische Tätigkeiten: maskenbildner</t>
         </is>
       </c>
-      <c r="J99" t="inlineStr">
+      <c r="J99" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
+      <c r="A100" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.synonym</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
+      <c r="B100" s="4" t="inlineStr">
         <is>
           <t>publizist</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
+      <c r="C100" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E100" t="n">
+      <c r="E100" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H100" t="inlineStr">
+      <c r="H100" s="4" t="inlineStr">
         <is>
           <t>Info-06</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr">
+      <c r="I100" s="4" t="inlineStr">
         <is>
           <t>KSK-Info 06, Stand 09.2025, S. 3, Katalog künstlerische/publizistische Tätigkeiten: publizist</t>
         </is>
       </c>
-      <c r="J100" t="inlineStr">
+      <c r="J100" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
+      <c r="A101" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.synonym</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
+      <c r="B101" s="4" t="inlineStr">
         <is>
           <t>reporter</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
+      <c r="C101" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E101" t="n">
+      <c r="E101" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H101" t="inlineStr">
+      <c r="H101" s="4" t="inlineStr">
         <is>
           <t>Info-06</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr">
+      <c r="I101" s="4" t="inlineStr">
         <is>
           <t>KSK-Info 06, Stand 09.2025, S. 3, Katalog künstlerische/publizistische Tätigkeiten: reporter</t>
         </is>
       </c>
-      <c r="J101" t="inlineStr">
+      <c r="J101" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr">
+      <c r="A102" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.synonym</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
+      <c r="B102" s="4" t="inlineStr">
         <is>
           <t>kritiker</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
+      <c r="C102" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E102" t="n">
+      <c r="E102" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H102" t="inlineStr">
+      <c r="H102" s="4" t="inlineStr">
         <is>
           <t>Info-06</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr">
+      <c r="I102" s="4" t="inlineStr">
         <is>
           <t>KSK-Info 06, Stand 09.2025, S. 3, Katalog künstlerische/publizistische Tätigkeiten: kritiker</t>
         </is>
       </c>
-      <c r="J102" t="inlineStr">
+      <c r="J102" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr">
+      <c r="A103" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.synonym</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
+      <c r="B103" s="4" t="inlineStr">
         <is>
           <t>herausgeber</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
+      <c r="C103" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E103" t="n">
+      <c r="E103" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H103" t="inlineStr">
+      <c r="H103" s="4" t="inlineStr">
         <is>
           <t>Info-06</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr">
+      <c r="I103" s="4" t="inlineStr">
         <is>
           <t>KSK-Info 06, Stand 09.2025, S. 3, Katalog künstlerische/publizistische Tätigkeiten: herausgeber</t>
         </is>
       </c>
-      <c r="J103" t="inlineStr">
+      <c r="J103" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr">
+      <c r="A104" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.synonym</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
+      <c r="B104" s="4" t="inlineStr">
         <is>
           <t>liedermacher</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
+      <c r="C104" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E104" t="n">
+      <c r="E104" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H104" t="inlineStr">
+      <c r="H104" s="4" t="inlineStr">
         <is>
           <t>Info-06</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr">
+      <c r="I104" s="4" t="inlineStr">
         <is>
           <t>KSK-Info 06, Stand 09.2025, S. 3, Katalog künstlerische/publizistische Tätigkeiten: liedermacher</t>
         </is>
       </c>
-      <c r="J104" t="inlineStr">
+      <c r="J104" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr">
+      <c r="A105" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.synonym</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
+      <c r="B105" s="4" t="inlineStr">
         <is>
           <t>songwriter</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
+      <c r="C105" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E105" t="n">
+      <c r="E105" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H105" t="inlineStr">
+      <c r="H105" s="4" t="inlineStr">
         <is>
           <t>Info-06</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr">
+      <c r="I105" s="4" t="inlineStr">
         <is>
           <t>KSK-Info 06, Stand 09.2025, S. 3, Katalog künstlerische/publizistische Tätigkeiten: songwriter</t>
         </is>
       </c>
-      <c r="J105" t="inlineStr">
+      <c r="J105" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr">
+      <c r="A106" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.synonym</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
+      <c r="B106" s="4" t="inlineStr">
         <is>
           <t>texter</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
+      <c r="C106" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E106" t="n">
+      <c r="E106" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H106" t="inlineStr">
+      <c r="H106" s="4" t="inlineStr">
         <is>
           <t>Info-06</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr">
+      <c r="I106" s="4" t="inlineStr">
         <is>
           <t>KSK-Info 06, Stand 09.2025, S. 3, Katalog künstlerische/publizistische Tätigkeiten: texter</t>
         </is>
       </c>
-      <c r="J106" t="inlineStr">
+      <c r="J106" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr">
+      <c r="A107" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.synonym</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
+      <c r="B107" s="4" t="inlineStr">
         <is>
           <t>layouter</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr">
+      <c r="C107" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E107" t="n">
+      <c r="E107" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H107" t="inlineStr">
+      <c r="H107" s="4" t="inlineStr">
         <is>
           <t>Info-06</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr">
+      <c r="I107" s="4" t="inlineStr">
         <is>
           <t>KSK-Info 06, Stand 09.2025, S. 3, Katalog künstlerische/publizistische Tätigkeiten: layouter</t>
         </is>
       </c>
-      <c r="J107" t="inlineStr">
+      <c r="J107" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr">
+      <c r="A108" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.synonym</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
+      <c r="B108" s="4" t="inlineStr">
         <is>
           <t>comiczeichner</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr">
+      <c r="C108" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E108" t="n">
+      <c r="E108" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H108" t="inlineStr">
+      <c r="H108" s="4" t="inlineStr">
         <is>
           <t>Info-06</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr">
+      <c r="I108" s="4" t="inlineStr">
         <is>
           <t>KSK-Info 06, Stand 09.2025, S. 3, Katalog künstlerische/publizistische Tätigkeiten: comiczeichner</t>
         </is>
       </c>
-      <c r="J108" t="inlineStr">
+      <c r="J108" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr">
+      <c r="A109" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.synonym</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
+      <c r="B109" s="4" t="inlineStr">
         <is>
           <t>karikaturist</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr">
+      <c r="C109" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E109" t="n">
+      <c r="E109" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H109" t="inlineStr">
+      <c r="H109" s="4" t="inlineStr">
         <is>
           <t>Info-06</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr">
+      <c r="I109" s="4" t="inlineStr">
         <is>
           <t>KSK-Info 06, Stand 09.2025, S. 3, Katalog künstlerische/publizistische Tätigkeiten: karikaturist</t>
         </is>
       </c>
-      <c r="J109" t="inlineStr">
+      <c r="J109" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr">
+      <c r="A110" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.synonym</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr">
+      <c r="B110" s="4" t="inlineStr">
         <is>
           <t>rezitator</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr">
+      <c r="C110" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E110" t="n">
+      <c r="E110" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H110" t="inlineStr">
+      <c r="H110" s="4" t="inlineStr">
         <is>
           <t>Info-06</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr">
+      <c r="I110" s="4" t="inlineStr">
         <is>
           <t>KSK-Info 06, Stand 09.2025, S. 3, Katalog künstlerische/publizistische Tätigkeiten: rezitator</t>
         </is>
       </c>
-      <c r="J110" t="inlineStr">
+      <c r="J110" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr">
+      <c r="A111" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.synonym</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr">
+      <c r="B111" s="4" t="inlineStr">
         <is>
           <t>drehbuchautor</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr">
+      <c r="C111" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E111" t="n">
+      <c r="E111" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H111" t="inlineStr">
+      <c r="H111" s="4" t="inlineStr">
         <is>
           <t>Info-06</t>
         </is>
       </c>
-      <c r="I111" t="inlineStr">
+      <c r="I111" s="4" t="inlineStr">
         <is>
           <t>KSK-Info 06, Stand 09.2025, S. 3, Katalog künstlerische/publizistische Tätigkeiten: drehbuchautor</t>
         </is>
       </c>
-      <c r="J111" t="inlineStr">
+      <c r="J111" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr">
+      <c r="A112" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.synonym</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr">
+      <c r="B112" s="4" t="inlineStr">
         <is>
           <t>filmemacher</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr">
+      <c r="C112" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E112" t="n">
+      <c r="E112" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H112" t="inlineStr">
+      <c r="H112" s="4" t="inlineStr">
         <is>
           <t>Info-06</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr">
+      <c r="I112" s="4" t="inlineStr">
         <is>
           <t>KSK-Info 06, Stand 09.2025, S. 3, Katalog künstlerische/publizistische Tätigkeiten: filmemacher</t>
         </is>
       </c>
-      <c r="J112" t="inlineStr">
+      <c r="J112" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr">
+      <c r="A113" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.synonym</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr">
+      <c r="B113" s="4" t="inlineStr">
         <is>
           <t>regisseur</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr">
+      <c r="C113" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E113" t="n">
+      <c r="E113" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H113" t="inlineStr">
+      <c r="H113" s="4" t="inlineStr">
         <is>
           <t>Info-06</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr">
+      <c r="I113" s="4" t="inlineStr">
         <is>
           <t>KSK-Info 06, Stand 09.2025, S. 3, Katalog künstlerische/publizistische Tätigkeiten: regisseur</t>
         </is>
       </c>
-      <c r="J113" t="inlineStr">
+      <c r="J113" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr">
+      <c r="A114" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.synonym</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr">
+      <c r="B114" s="4" t="inlineStr">
         <is>
           <t>komponist</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr">
+      <c r="C114" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E114" t="n">
+      <c r="E114" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H114" t="inlineStr">
+      <c r="H114" s="4" t="inlineStr">
         <is>
           <t>Info-06</t>
         </is>
       </c>
-      <c r="I114" t="inlineStr">
+      <c r="I114" s="4" t="inlineStr">
         <is>
           <t>KSK-Info 06, Stand 09.2025, S. 3, Katalog künstlerische/publizistische Tätigkeiten: komponist</t>
         </is>
       </c>
-      <c r="J114" t="inlineStr">
+      <c r="J114" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr">
+      <c r="A115" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.synonym</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr">
+      <c r="B115" s="4" t="inlineStr">
         <is>
           <t>autor</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr">
+      <c r="C115" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E115" t="n">
+      <c r="E115" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H115" t="inlineStr">
+      <c r="H115" s="4" t="inlineStr">
         <is>
           <t>Info-06</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr">
+      <c r="I115" s="4" t="inlineStr">
         <is>
           <t>KSK-Info 06, Stand 09.2025, S. 3, Katalog künstlerische/publizistische Tätigkeiten: autor</t>
         </is>
       </c>
-      <c r="J115" t="inlineStr">
+      <c r="J115" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr">
+      <c r="A116" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.synonym</t>
         </is>
       </c>
-      <c r="B116" t="inlineStr">
+      <c r="B116" s="4" t="inlineStr">
         <is>
           <t>pressefotograf</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr">
+      <c r="C116" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E116" t="n">
+      <c r="E116" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H116" t="inlineStr">
+      <c r="H116" s="4" t="inlineStr">
         <is>
           <t>Info-06</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr">
+      <c r="I116" s="4" t="inlineStr">
         <is>
           <t>KSK-Info 06, Stand 09.2025, S. 3, Katalog künstlerische/publizistische Tätigkeiten: pressefotograf</t>
         </is>
       </c>
-      <c r="J116" t="inlineStr">
+      <c r="J116" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr">
+      <c r="A117" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.synonym</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr">
+      <c r="B117" s="4" t="inlineStr">
         <is>
           <t>werbefotograf</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr">
+      <c r="C117" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E117" t="n">
+      <c r="E117" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H117" t="inlineStr">
+      <c r="H117" s="4" t="inlineStr">
         <is>
           <t>Info-06</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr">
+      <c r="I117" s="4" t="inlineStr">
         <is>
           <t>KSK-Info 06, Stand 09.2025, S. 3, Katalog künstlerische/publizistische Tätigkeiten: werbefotograf</t>
         </is>
       </c>
-      <c r="J117" t="inlineStr">
+      <c r="J117" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr">
+      <c r="A118" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.synonym</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr">
+      <c r="B118" s="4" t="inlineStr">
         <is>
           <t>game-designer</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr">
+      <c r="C118" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E118" t="n">
+      <c r="E118" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H118" t="inlineStr">
+      <c r="H118" s="4" t="inlineStr">
         <is>
           <t>Info-06</t>
         </is>
       </c>
-      <c r="I118" t="inlineStr">
+      <c r="I118" s="4" t="inlineStr">
         <is>
           <t>KSK-Info 06, Stand 09.2025, S. 3, Katalog künstlerische/publizistische Tätigkeiten: game-designer</t>
         </is>
       </c>
-      <c r="J118" t="inlineStr">
+      <c r="J118" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr">
+      <c r="A119" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.synonym</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr">
+      <c r="B119" s="4" t="inlineStr">
         <is>
           <t>corporate-design</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr">
+      <c r="C119" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E119" t="n">
+      <c r="E119" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H119" t="inlineStr">
+      <c r="H119" s="4" t="inlineStr">
         <is>
           <t>Info-02</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr">
+      <c r="I119" s="4" t="inlineStr">
         <is>
           <t>KSK-Info 02, S. 1, Abschnitt 4: Corporate-Design ist eine Design-Leistung, die vom KSVG erfasst ist.</t>
         </is>
       </c>
-      <c r="J119" t="inlineStr">
+      <c r="J119" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr">
+      <c r="A120" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.offen</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr">
+      <c r="B120" s="4" t="inlineStr">
         <is>
           <t>übersetzung</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr">
+      <c r="C120" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E120" t="n">
+      <c r="E120" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H120" t="inlineStr">
+      <c r="H120" s="4" t="inlineStr">
         <is>
           <t>Info-06-Offen</t>
         </is>
       </c>
-      <c r="I120" t="inlineStr">
+      <c r="I120" s="4" t="inlineStr">
         <is>
           <t>KSK-Info 06, S. 3: Übersetzer/Bearbeiter mit Fussnote * (Besonderheiten, schriftlich bei der KSK anfragen). Literarisch oder Fachübersetzung entscheidet der Einzelfall.</t>
         </is>
       </c>
-      <c r="J120" t="inlineStr">
+      <c r="J120" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr">
+      <c r="A121" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.offen</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr">
+      <c r="B121" s="4" t="inlineStr">
         <is>
           <t>übersetzer</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr">
+      <c r="C121" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E121" t="n">
+      <c r="E121" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H121" t="inlineStr">
+      <c r="H121" s="4" t="inlineStr">
         <is>
           <t>Info-06-Offen</t>
         </is>
       </c>
-      <c r="I121" t="inlineStr">
+      <c r="I121" s="4" t="inlineStr">
         <is>
           <t>KSK-Info 06, S. 3: Übersetzer/Bearbeiter mit Fussnote *. Keine stille Wahl zwischen literarisch und Fachübersetzung.</t>
         </is>
       </c>
-      <c r="J121" t="inlineStr">
+      <c r="J121" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr">
+      <c r="A122" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.offen</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr">
+      <c r="B122" s="4" t="inlineStr">
         <is>
           <t>übersetzerin</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr">
+      <c r="C122" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E122" t="n">
+      <c r="E122" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H122" t="inlineStr">
+      <c r="H122" s="4" t="inlineStr">
         <is>
           <t>Info-06-Offen</t>
         </is>
       </c>
-      <c r="I122" t="inlineStr">
+      <c r="I122" s="4" t="inlineStr">
         <is>
           <t>KSK-Info 06, S. 3: Übersetzer/Bearbeiter mit Fussnote *. Keine stille Wahl zwischen literarisch und Fachübersetzung.</t>
         </is>
       </c>
-      <c r="J122" t="inlineStr">
+      <c r="J122" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="inlineStr">
+      <c r="A123" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.offen</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr">
+      <c r="B123" s="4" t="inlineStr">
         <is>
           <t>uebersetzung</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr">
+      <c r="C123" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E123" t="n">
+      <c r="E123" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H123" t="inlineStr">
+      <c r="H123" s="4" t="inlineStr">
         <is>
           <t>Info-06-Offen</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr">
+      <c r="I123" s="4" t="inlineStr">
         <is>
           <t>KSK-Info 06, S. 3: Übersetzer/Bearbeiter mit Fussnote *. Keine stille Wahl zwischen literarisch und Fachübersetzung.</t>
         </is>
       </c>
-      <c r="J123" t="inlineStr">
+      <c r="J123" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="inlineStr">
+      <c r="A124" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.offen</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr">
+      <c r="B124" s="4" t="inlineStr">
         <is>
           <t>uebersetzer</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr">
+      <c r="C124" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E124" t="n">
+      <c r="E124" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H124" t="inlineStr">
+      <c r="H124" s="4" t="inlineStr">
         <is>
           <t>Info-06-Offen</t>
         </is>
       </c>
-      <c r="I124" t="inlineStr">
+      <c r="I124" s="4" t="inlineStr">
         <is>
           <t>KSK-Info 06, S. 3: Übersetzer/Bearbeiter mit Fussnote *. Keine stille Wahl zwischen literarisch und Fachübersetzung.</t>
         </is>
       </c>
-      <c r="J124" t="inlineStr">
+      <c r="J124" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="inlineStr">
+      <c r="A125" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.offen</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr">
+      <c r="B125" s="4" t="inlineStr">
         <is>
           <t>kunstunterricht</t>
         </is>
       </c>
-      <c r="C125" t="inlineStr">
+      <c r="C125" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E125" t="n">
+      <c r="E125" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H125" t="inlineStr">
+      <c r="H125" s="4" t="inlineStr">
         <is>
           <t>Info-06-Offen</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr">
+      <c r="I125" s="4" t="inlineStr">
         <is>
           <t>KSK-Info 06, S. 1: Künstler ist auch, wer Kunst lehrt; S. 2 nennt Lehrer für künstlerische Tätigkeiten. Ob die konkrete Stunde nur Unterricht ist, sagt der Katalog nicht.</t>
         </is>
       </c>
-      <c r="J125" t="inlineStr">
+      <c r="J125" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr">
+      <c r="A126" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.offen</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr">
+      <c r="B126" s="4" t="inlineStr">
         <is>
           <t>gesangsunterricht</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr">
+      <c r="C126" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E126" t="n">
+      <c r="E126" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H126" t="inlineStr">
+      <c r="H126" s="4" t="inlineStr">
         <is>
           <t>Info-06-Offen</t>
         </is>
       </c>
-      <c r="I126" t="inlineStr">
+      <c r="I126" s="4" t="inlineStr">
         <is>
           <t>KSK-Info 06, S. 3 nennt Musiklehrer, nicht die einzelne Gesangsstunde. Darbietung oder pädagogische Vermittlung bleibt Einzelfall.</t>
         </is>
       </c>
-      <c r="J126" t="inlineStr">
+      <c r="J126" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr">
+      <c r="A127" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.offen</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr">
+      <c r="B127" s="4" t="inlineStr">
         <is>
           <t>stimmcoaching</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr">
+      <c r="C127" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E127" t="n">
+      <c r="E127" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H127" t="inlineStr">
+      <c r="H127" s="4" t="inlineStr">
         <is>
           <t>Info-06-Offen</t>
         </is>
       </c>
-      <c r="I127" t="inlineStr">
+      <c r="I127" s="4" t="inlineStr">
         <is>
           <t>KSK-Info 06 nennt Sprecherzieher und Musiklehrer, nicht Stimmcoaching. Pädagogische Vermittlung oder Darbietung ist nicht entschieden.</t>
         </is>
       </c>
-      <c r="J127" t="inlineStr">
+      <c r="J127" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr">
+      <c r="A128" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.offen</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr">
+      <c r="B128" s="4" t="inlineStr">
         <is>
           <t>lektor</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr">
+      <c r="C128" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E128" t="n">
+      <c r="E128" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H128" t="inlineStr">
+      <c r="H128" s="4" t="inlineStr">
         <is>
           <t>Info-06-Offen</t>
         </is>
       </c>
-      <c r="I128" t="inlineStr">
+      <c r="I128" s="4" t="inlineStr">
         <is>
           <t>KSK-Info 06, S. 2 führt Lektor auf. Info 09, S. 4, Abschnitt 3.2: bei mehreren Leistungsanteilen entscheidet der überwiegende Teil. Kein Automatismus.</t>
         </is>
       </c>
-      <c r="J128" t="inlineStr">
+      <c r="J128" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr">
+      <c r="A129" s="4" t="inlineStr">
         <is>
           <t>taetigkeit.offen</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr">
+      <c r="B129" s="4" t="inlineStr">
         <is>
           <t>lektorat</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr">
+      <c r="C129" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E129" t="n">
+      <c r="E129" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H129" t="inlineStr">
+      <c r="H129" s="4" t="inlineStr">
         <is>
           <t>Info-06-Offen</t>
         </is>
       </c>
-      <c r="I129" t="inlineStr">
+      <c r="I129" s="4" t="inlineStr">
         <is>
           <t>KSK-Info 06, S. 2 führt Lektor auf. Info 09, S. 4, Abschnitt 3.2: bei mehreren Leistungsanteilen entscheidet der überwiegende Teil. Kein Automatismus.</t>
         </is>
       </c>
-      <c r="J129" t="inlineStr">
+      <c r="J129" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="A130" t="inlineStr">
+      <c r="A130" s="4" t="inlineStr">
         <is>
           <t>ausland.kuenstler</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr">
+      <c r="B130" s="4" t="inlineStr">
         <is>
           <t>ausländisch</t>
         </is>
       </c>
-      <c r="C130" t="inlineStr">
+      <c r="C130" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E130" t="n">
+      <c r="E130" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H130" t="inlineStr">
+      <c r="H130" s="4" t="inlineStr">
         <is>
           <t>Info-22</t>
         </is>
       </c>
-      <c r="I130" t="inlineStr">
+      <c r="I130" s="4" t="inlineStr">
         <is>
           <t>KSK-Info 22, Stand 10.2025, S. 1-2, Abschn. 2 und 6: Abgabe auf selbständige ausländische Künstler ja, abhängige Beschäftigung und A1-Bescheinigung nein. Status nach deutschem Recht ist zu klären.</t>
         </is>
       </c>
-      <c r="J130" t="inlineStr">
+      <c r="J130" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" t="inlineStr">
+      <c r="A131" s="4" t="inlineStr">
         <is>
           <t>ausland.kuenstler</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr">
+      <c r="B131" s="4" t="inlineStr">
         <is>
           <t>auslaendisch</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr">
+      <c r="C131" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E131" t="n">
+      <c r="E131" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H131" t="inlineStr">
+      <c r="H131" s="4" t="inlineStr">
         <is>
           <t>Info-22</t>
         </is>
       </c>
-      <c r="I131" t="inlineStr">
+      <c r="I131" s="4" t="inlineStr">
         <is>
           <t>KSK-Info 22, Stand 10.2025, S. 1-2, Abschn. 6: Die KSK prüft selbständige oder abhängige Tätigkeit nach deutschem Recht. Bescheinigungen des Auslands sind kein Nachweis.</t>
         </is>
       </c>
-      <c r="J131" t="inlineStr">
+      <c r="J131" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="inlineStr">
+      <c r="A132" s="4" t="inlineStr">
         <is>
           <t>ausland.kuenstler</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr">
+      <c r="B132" s="4" t="inlineStr">
         <is>
           <t>auslandssachverhalt</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr">
+      <c r="C132" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E132" t="n">
+      <c r="E132" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H132" t="inlineStr">
+      <c r="H132" s="4" t="inlineStr">
         <is>
           <t>Info-22</t>
         </is>
       </c>
-      <c r="I132" t="inlineStr">
+      <c r="I132" s="4" t="inlineStr">
         <is>
           <t>KSK-Info 22, Stand 10.2025, S. 1 Abschn. 2: Auslandsbezug hebt die Abgabe nicht auf. Ob ein abhängiges Beschäftigungsverhältnis vorliegt, ist zu klären.</t>
         </is>
       </c>
-      <c r="J132" t="inlineStr">
+      <c r="J132" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr">
+      <c r="A133" s="4" t="inlineStr">
         <is>
           <t>gemeinnuetzig</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr">
+      <c r="B133" s="4" t="inlineStr">
         <is>
           <t>gemeinnützig</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr">
+      <c r="C133" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E133" t="n">
+      <c r="E133" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H133" t="inlineStr">
+      <c r="H133" s="4" t="inlineStr">
         <is>
           <t>Info-23</t>
         </is>
       </c>
-      <c r="I133" t="inlineStr">
+      <c r="I133" s="4" t="inlineStr">
         <is>
           <t>KSK-Info 23, Stand 01.2026, S. 1 Abschn. 2: Gemeinnützigkeit befreit nicht und begründet die Abgabe nicht allein. Befreiungstatbestände sind nicht vorgesehen.</t>
         </is>
       </c>
-      <c r="J133" t="inlineStr">
+      <c r="J133" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="A134" t="inlineStr">
+      <c r="A134" s="4" t="inlineStr">
         <is>
           <t>gemeinnuetzig</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr">
+      <c r="B134" s="4" t="inlineStr">
         <is>
           <t>gemeinnuetzig</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr">
+      <c r="C134" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E134" t="n">
+      <c r="E134" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H134" t="inlineStr">
+      <c r="H134" s="4" t="inlineStr">
         <is>
           <t>Info-23</t>
         </is>
       </c>
-      <c r="I134" t="inlineStr">
+      <c r="I134" s="4" t="inlineStr">
         <is>
           <t>KSK-Info 23, Stand 01.2026, S. 1 Abschn. 2: Gemeinnützigkeit befreit nicht und begründet die Abgabe nicht allein.</t>
         </is>
       </c>
-      <c r="J134" t="inlineStr">
+      <c r="J134" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="inlineStr">
+      <c r="A135" s="4" t="inlineStr">
         <is>
           <t>auftraggeber.kommune</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr">
+      <c r="B135" s="4" t="inlineStr">
         <is>
           <t>stadt</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr">
+      <c r="C135" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E135" t="n">
+      <c r="E135" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H135" t="inlineStr">
+      <c r="H135" s="4" t="inlineStr">
         <is>
           <t>Info-11</t>
         </is>
       </c>
-      <c r="I135" t="inlineStr">
+      <c r="I135" s="4" t="inlineStr">
         <is>
           <t>KSK-Info 11, Stand der Datei, S. 1 Abschn. 1-2: Städte, Landkreise und Gemeinden können abgabepflichtig sein. Das ist kein Ausschluss wie eine Zahlung an eine öffentliche Körperschaft als Empfänger.</t>
         </is>
       </c>
-      <c r="J135" t="inlineStr">
+      <c r="J135" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="A136" t="inlineStr">
+      <c r="A136" s="4" t="inlineStr">
         <is>
           <t>auftraggeber.kommune</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr">
+      <c r="B136" s="4" t="inlineStr">
         <is>
           <t>landkreis</t>
         </is>
       </c>
-      <c r="C136" t="inlineStr">
+      <c r="C136" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E136" t="n">
+      <c r="E136" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H136" t="inlineStr">
+      <c r="H136" s="4" t="inlineStr">
         <is>
           <t>Info-11</t>
         </is>
       </c>
-      <c r="I136" t="inlineStr">
+      <c r="I136" s="4" t="inlineStr">
         <is>
           <t>KSK-Info 11, Stand der Datei, S. 1 Abschn. 1-2: Städte, Landkreise und Gemeinden können abgabepflichtig sein. Das ist kein Ausschluss wie eine Zahlung an eine öffentliche Körperschaft als Empfänger.</t>
         </is>
       </c>
-      <c r="J136" t="inlineStr">
+      <c r="J136" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="137">
-      <c r="A137" t="inlineStr">
+      <c r="A137" s="4" t="inlineStr">
         <is>
           <t>auftraggeber.kommune</t>
         </is>
       </c>
-      <c r="B137" t="inlineStr">
+      <c r="B137" s="4" t="inlineStr">
         <is>
           <t>gemeinde</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr">
+      <c r="C137" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E137" t="n">
+      <c r="E137" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H137" t="inlineStr">
+      <c r="H137" s="4" t="inlineStr">
         <is>
           <t>Info-11</t>
         </is>
       </c>
-      <c r="I137" t="inlineStr">
+      <c r="I137" s="4" t="inlineStr">
         <is>
           <t>KSK-Info 11, Stand der Datei, S. 1 Abschn. 1-2: Städte, Landkreise und Gemeinden können abgabepflichtig sein. Das ist kein Ausschluss wie eine Zahlung an eine öffentliche Körperschaft als Empfänger.</t>
         </is>
       </c>
-      <c r="J137" t="inlineStr">
+      <c r="J137" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="inlineStr">
+      <c r="A138" s="4" t="inlineStr">
         <is>
           <t>gesellschafter.gmbh</t>
         </is>
       </c>
-      <c r="B138" t="inlineStr">
+      <c r="B138" s="4" t="inlineStr">
         <is>
           <t>gesellschafter</t>
         </is>
       </c>
-      <c r="C138" t="inlineStr">
+      <c r="C138" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E138" t="n">
+      <c r="E138" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H138" t="inlineStr">
+      <c r="H138" s="4" t="inlineStr">
         <is>
           <t>Gesellschafter</t>
         </is>
       </c>
-      <c r="I138" t="inlineStr">
+      <c r="I138" s="4" t="inlineStr">
         <is>
           <t>KSK-Merkblatt Gesellschafter einer GmbH, S. 1-2: Mitarbeitender Gesellschafter ist nur bei maßgeblichem Einfluss selbständig. Künstlerischer Anteil und Oberleitung prüft die KSK. BSG 16.04.1998, B 3 KR 7/97 R, im Merkblatt zitiert.</t>
         </is>
       </c>
-      <c r="J138" t="inlineStr">
+      <c r="J138" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="inlineStr">
+      <c r="A139" s="4" t="inlineStr">
         <is>
           <t>musikverein.schueler_unter</t>
         </is>
       </c>
-      <c r="B139" t="inlineStr">
+      <c r="B139" s="4" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr">
+      <c r="C139" s="4" t="inlineStr">
         <is>
           <t>Schüler</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr">
+      <c r="D139" s="4" t="inlineStr">
         <is>
           <t>&lt;=</t>
         </is>
       </c>
-      <c r="E139" t="n">
+      <c r="E139" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H139" t="inlineStr">
+      <c r="H139" s="4" t="inlineStr">
         <is>
           <t>Info-12-P1</t>
         </is>
       </c>
-      <c r="I139" t="inlineStr">
+      <c r="I139" s="4" t="inlineStr">
         <is>
           <t>KSK-Info 12, Stand 01.2026, S. 2 Punkt 1: nicht mehr als 20 Schüler, dem Grunde nach keine Abgabepflicht nach § 24 Abs. 1 Nr. 9 KSVG.</t>
         </is>
       </c>
-      <c r="J139" t="inlineStr">
+      <c r="J139" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" t="inlineStr">
+      <c r="A140" s="4" t="inlineStr">
         <is>
           <t>musikverein.schueler_mitte</t>
         </is>
       </c>
-      <c r="B140" t="inlineStr">
+      <c r="B140" s="4" t="inlineStr">
         <is>
           <t>vermutung</t>
         </is>
       </c>
-      <c r="C140" t="inlineStr">
+      <c r="C140" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E140" t="n">
+      <c r="E140" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H140" t="inlineStr">
+      <c r="H140" s="4" t="inlineStr">
         <is>
           <t>Info-12-P2</t>
         </is>
       </c>
-      <c r="I140" t="inlineStr">
+      <c r="I140" s="4" t="inlineStr">
         <is>
           <t>KSK-Info 12, Stand 01.2026, S. 2 Punkt 2: mehr als 20 und weniger als 61 Schüler, Vermutung keine Abgabepflicht nach § 24 Abs. 1 Nr. 9, wenn kein Ausbilder über der Übungsleiterpauschale liegt.</t>
         </is>
       </c>
-      <c r="J140" t="inlineStr">
+      <c r="J140" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="141">
-      <c r="A141" t="inlineStr">
+      <c r="A141" s="4" t="inlineStr">
         <is>
           <t>entgelt.ausgenommen</t>
         </is>
       </c>
-      <c r="B141" t="inlineStr">
+      <c r="B141" s="4" t="inlineStr">
         <is>
           <t>gema</t>
         </is>
       </c>
-      <c r="C141" t="inlineStr">
+      <c r="C141" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E141" t="n">
+      <c r="E141" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H141" t="inlineStr">
+      <c r="H141" s="4" t="inlineStr">
         <is>
           <t>KSVG-25</t>
         </is>
       </c>
-      <c r="I141" t="inlineStr">
+      <c r="I141" s="4" t="inlineStr">
         <is>
           <t>KSVG § 25 Abs. 2: Entgelte für Nutzungsrechte an Verwertungsgesellschaften sind ausgenommen (Gesetzestext im Repo, Seite 9).</t>
         </is>
       </c>
-      <c r="J141" t="inlineStr">
+      <c r="J141" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" t="inlineStr">
+      <c r="A142" s="4" t="inlineStr">
         <is>
           <t>entgelt.ausgenommen</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr">
+      <c r="B142" s="4" t="inlineStr">
         <is>
           <t>verwertungsgesellschaft</t>
         </is>
       </c>
-      <c r="C142" t="inlineStr">
+      <c r="C142" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E142" t="n">
+      <c r="E142" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H142" t="inlineStr">
+      <c r="H142" s="4" t="inlineStr">
         <is>
           <t>KSVG-25</t>
         </is>
       </c>
-      <c r="I142" t="inlineStr">
+      <c r="I142" s="4" t="inlineStr">
         <is>
           <t>KSVG § 25 Abs. 2 Nr. 1: Entgelte an Verwertungsgesellschaften für urheberrechtliche Nutzungsrechte gehören nicht zum Entgelt.</t>
         </is>
       </c>
-      <c r="J142" t="inlineStr">
+      <c r="J142" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="143">
-      <c r="A143" t="inlineStr">
+      <c r="A143" s="4" t="inlineStr">
         <is>
           <t>entgelt.ausgenommen</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr">
+      <c r="B143" s="4" t="inlineStr">
         <is>
           <t>verwertung</t>
         </is>
       </c>
-      <c r="C143" t="inlineStr">
+      <c r="C143" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E143" t="n">
+      <c r="E143" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H143" t="inlineStr">
+      <c r="H143" s="4" t="inlineStr">
         <is>
           <t>KSVG-25</t>
         </is>
       </c>
-      <c r="I143" t="inlineStr">
+      <c r="I143" s="4" t="inlineStr">
         <is>
           <t>KSVG § 25 Abs. 2 Nr. 1: Zahlung wegen Verwertung an eine Verwertungsgesellschaft, nicht schon jede Verlagsleistung.</t>
         </is>
       </c>
-      <c r="J143" t="inlineStr">
+      <c r="J143" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="144">
-      <c r="A144" t="inlineStr">
+      <c r="A144" s="4" t="inlineStr">
         <is>
           <t>entgelt.ausgenommen</t>
         </is>
       </c>
-      <c r="B144" t="inlineStr">
+      <c r="B144" s="4" t="inlineStr">
         <is>
           <t>musikverlag</t>
         </is>
       </c>
-      <c r="C144" t="inlineStr">
+      <c r="C144" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E144" t="n">
+      <c r="E144" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H144" t="inlineStr">
+      <c r="H144" s="4" t="inlineStr">
         <is>
           <t>KSVG-25</t>
         </is>
       </c>
-      <c r="I144" t="inlineStr">
+      <c r="I144" s="4" t="inlineStr">
         <is>
           <t>KSK-Checkliste Verlage und KSVG § 25 Abs. 2 Nr. 1: Lizenzzahlung, die als Verwertung ausgewiesen ist. Ein Verlag ist nicht schon deshalb eine Verwertungsgesellschaft.</t>
         </is>
       </c>
-      <c r="J144" t="inlineStr">
+      <c r="J144" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="145">
-      <c r="A145" t="inlineStr">
+      <c r="A145" s="4" t="inlineStr">
         <is>
           <t>auslage.mit_beleg_ausgenommen</t>
         </is>
       </c>
-      <c r="B145" t="inlineStr">
+      <c r="B145" s="4" t="inlineStr">
         <is>
           <t>reise</t>
         </is>
       </c>
-      <c r="C145" t="inlineStr">
+      <c r="C145" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E145" t="n">
+      <c r="E145" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H145" t="inlineStr">
+      <c r="H145" s="4" t="inlineStr">
         <is>
           <t>KSVEntgV-1</t>
         </is>
       </c>
-      <c r="I145" t="inlineStr">
+      <c r="I145" s="4" t="inlineStr">
         <is>
           <t>KSVEntgV § 1 Nr. 1: nachgewiesene Reisekosten innerhalb der Grenzen des § 3 Nr. 16 EStG zählen nicht. KSK-Info 10, S. 2.</t>
         </is>
       </c>
-      <c r="J145" t="inlineStr">
+      <c r="J145" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" t="inlineStr">
+      <c r="A146" s="4" t="inlineStr">
         <is>
           <t>auslage.mit_beleg_ausgenommen</t>
         </is>
       </c>
-      <c r="B146" t="inlineStr">
+      <c r="B146" s="4" t="inlineStr">
         <is>
           <t>fahrt</t>
         </is>
       </c>
-      <c r="C146" t="inlineStr">
+      <c r="C146" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E146" t="n">
+      <c r="E146" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H146" t="inlineStr">
+      <c r="H146" s="4" t="inlineStr">
         <is>
           <t>KSVEntgV-1</t>
         </is>
       </c>
-      <c r="I146" t="inlineStr">
+      <c r="I146" s="4" t="inlineStr">
         <is>
           <t>KSVEntgV § 1 Nr. 1: nachgewiesene Reisekosten innerhalb der Grenzen des § 3 Nr. 16 EStG zählen nicht. KSK-Info 10, S. 2.</t>
         </is>
       </c>
-      <c r="J146" t="inlineStr">
+      <c r="J146" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="147">
-      <c r="A147" t="inlineStr">
+      <c r="A147" s="4" t="inlineStr">
         <is>
           <t>auslage.mit_beleg_ausgenommen</t>
         </is>
       </c>
-      <c r="B147" t="inlineStr">
+      <c r="B147" s="4" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="C147" t="inlineStr">
+      <c r="C147" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E147" t="n">
+      <c r="E147" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H147" t="inlineStr">
+      <c r="H147" s="4" t="inlineStr">
         <is>
           <t>KSVEntgV-1</t>
         </is>
       </c>
-      <c r="I147" t="inlineStr">
+      <c r="I147" s="4" t="inlineStr">
         <is>
           <t>KSVEntgV § 1 Nr. 1: nachgewiesene Reisekosten innerhalb der Grenzen des § 3 Nr. 16 EStG zählen nicht. KSK-Info 10, S. 2.</t>
         </is>
       </c>
-      <c r="J147" t="inlineStr">
+      <c r="J147" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="148">
-      <c r="A148" t="inlineStr">
+      <c r="A148" s="4" t="inlineStr">
         <is>
           <t>auslage.mit_beleg_ausgenommen</t>
         </is>
       </c>
-      <c r="B148" t="inlineStr">
+      <c r="B148" s="4" t="inlineStr">
         <is>
           <t>übernachtung</t>
         </is>
       </c>
-      <c r="C148" t="inlineStr">
+      <c r="C148" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E148" t="n">
+      <c r="E148" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H148" t="inlineStr">
+      <c r="H148" s="4" t="inlineStr">
         <is>
           <t>KSVEntgV-1</t>
         </is>
       </c>
-      <c r="I148" t="inlineStr">
+      <c r="I148" s="4" t="inlineStr">
         <is>
           <t>KSVEntgV § 1 Nr. 1: nachgewiesene Reisekosten innerhalb der Grenzen des § 3 Nr. 16 EStG zählen nicht. KSK-Info 10, S. 2.</t>
         </is>
       </c>
-      <c r="J148" t="inlineStr">
+      <c r="J148" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="149">
-      <c r="A149" t="inlineStr">
+      <c r="A149" s="4" t="inlineStr">
         <is>
           <t>auslage.mit_beleg_ausgenommen</t>
         </is>
       </c>
-      <c r="B149" t="inlineStr">
+      <c r="B149" s="4" t="inlineStr">
         <is>
           <t>uebernachtung</t>
         </is>
       </c>
-      <c r="C149" t="inlineStr">
+      <c r="C149" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E149" t="n">
+      <c r="E149" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H149" t="inlineStr">
+      <c r="H149" s="4" t="inlineStr">
         <is>
           <t>KSVEntgV-1</t>
         </is>
       </c>
-      <c r="I149" t="inlineStr">
+      <c r="I149" s="4" t="inlineStr">
         <is>
           <t>KSVEntgV § 1 Nr. 1: nachgewiesene Reisekosten innerhalb der Grenzen des § 3 Nr. 16 EStG zählen nicht. KSK-Info 10, S. 2.</t>
         </is>
       </c>
-      <c r="J149" t="inlineStr">
+      <c r="J149" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="150">
-      <c r="A150" t="inlineStr">
+      <c r="A150" s="4" t="inlineStr">
         <is>
           <t>auslage.mit_beleg_ausgenommen</t>
         </is>
       </c>
-      <c r="B150" t="inlineStr">
+      <c r="B150" s="4" t="inlineStr">
         <is>
           <t>verpflegung</t>
         </is>
       </c>
-      <c r="C150" t="inlineStr">
+      <c r="C150" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E150" t="n">
+      <c r="E150" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H150" t="inlineStr">
+      <c r="H150" s="4" t="inlineStr">
         <is>
           <t>KSVEntgV-1</t>
         </is>
       </c>
-      <c r="I150" t="inlineStr">
+      <c r="I150" s="4" t="inlineStr">
         <is>
           <t>KSVEntgV § 1 Nr. 1: nachgewiesene Reisekosten innerhalb der Grenzen des § 3 Nr. 16 EStG zählen nicht. KSK-Info 10, S. 2.</t>
         </is>
       </c>
-      <c r="J150" t="inlineStr">
+      <c r="J150" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="151">
-      <c r="A151" t="inlineStr">
+      <c r="A151" s="4" t="inlineStr">
         <is>
           <t>auslage.mit_beleg_ausgenommen</t>
         </is>
       </c>
-      <c r="B151" t="inlineStr">
+      <c r="B151" s="4" t="inlineStr">
         <is>
           <t>bewirtung</t>
         </is>
       </c>
-      <c r="C151" t="inlineStr">
+      <c r="C151" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E151" t="n">
+      <c r="E151" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H151" t="inlineStr">
+      <c r="H151" s="4" t="inlineStr">
         <is>
           <t>KSVEntgV-1</t>
         </is>
       </c>
-      <c r="I151" t="inlineStr">
+      <c r="I151" s="4" t="inlineStr">
         <is>
           <t>KSVEntgV § 1 und KSK-Info 10: nur die dort genannten nachgewiesenen Nebenleistungen fallen aus der Bemessung. Beleg erforderlich.</t>
         </is>
       </c>
-      <c r="J151" t="inlineStr">
+      <c r="J151" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="152">
-      <c r="A152" t="inlineStr">
+      <c r="A152" s="4" t="inlineStr">
         <is>
           <t>auslage.mit_beleg_ausgenommen</t>
         </is>
       </c>
-      <c r="B152" t="inlineStr">
+      <c r="B152" s="4" t="inlineStr">
         <is>
           <t>auslage</t>
         </is>
       </c>
-      <c r="C152" t="inlineStr">
+      <c r="C152" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E152" t="n">
+      <c r="E152" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H152" t="inlineStr">
+      <c r="H152" s="4" t="inlineStr">
         <is>
           <t>KSVEntgV-1</t>
         </is>
       </c>
-      <c r="I152" t="inlineStr">
+      <c r="I152" s="4" t="inlineStr">
         <is>
           <t>KSVEntgV § 1 und KSK-Info 10: nur die dort genannten nachgewiesenen Nebenleistungen fallen aus der Bemessung. Beleg erforderlich.</t>
         </is>
       </c>
-      <c r="J152" t="inlineStr">
+      <c r="J152" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="153">
-      <c r="A153" t="inlineStr">
+      <c r="A153" s="4" t="inlineStr">
         <is>
           <t>auslage.mit_beleg_ausgenommen</t>
         </is>
       </c>
-      <c r="B153" t="inlineStr">
+      <c r="B153" s="4" t="inlineStr">
         <is>
           <t>materialkosten</t>
         </is>
       </c>
-      <c r="C153" t="inlineStr">
+      <c r="C153" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E153" t="n">
+      <c r="E153" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H153" t="inlineStr">
+      <c r="H153" s="4" t="inlineStr">
         <is>
           <t>KSVEntgV-1</t>
         </is>
       </c>
-      <c r="I153" t="inlineStr">
+      <c r="I153" s="4" t="inlineStr">
         <is>
           <t>KSVEntgV § 1 und KSK-Info 10: nur die dort genannten nachgewiesenen Nebenleistungen fallen aus der Bemessung. Beleg erforderlich.</t>
         </is>
       </c>
-      <c r="J153" t="inlineStr">
+      <c r="J153" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="154">
-      <c r="A154" t="inlineStr">
+      <c r="A154" s="4" t="inlineStr">
         <is>
           <t>auslage.mit_beleg_ausgenommen</t>
         </is>
       </c>
-      <c r="B154" t="inlineStr">
+      <c r="B154" s="4" t="inlineStr">
         <is>
           <t>notenmappe</t>
         </is>
       </c>
-      <c r="C154" t="inlineStr">
+      <c r="C154" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E154" t="n">
+      <c r="E154" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H154" t="inlineStr">
+      <c r="H154" s="4" t="inlineStr">
         <is>
           <t>KSVEntgV-1</t>
         </is>
       </c>
-      <c r="I154" t="inlineStr">
+      <c r="I154" s="4" t="inlineStr">
         <is>
           <t>KSVEntgV § 1 und KSK-Info 10: nur die dort genannten nachgewiesenen Nebenleistungen fallen aus der Bemessung. Beleg erforderlich.</t>
         </is>
       </c>
-      <c r="J154" t="inlineStr">
+      <c r="J154" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="155">
-      <c r="A155" t="inlineStr">
+      <c r="A155" s="4" t="inlineStr">
         <is>
           <t>auslage.mit_beleg_ausgenommen</t>
         </is>
       </c>
-      <c r="B155" t="inlineStr">
+      <c r="B155" s="4" t="inlineStr">
         <is>
           <t>notenkauf</t>
         </is>
       </c>
-      <c r="C155" t="inlineStr">
+      <c r="C155" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E155" t="n">
+      <c r="E155" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H155" t="inlineStr">
+      <c r="H155" s="4" t="inlineStr">
         <is>
           <t>KSVEntgV-1</t>
         </is>
       </c>
-      <c r="I155" t="inlineStr">
+      <c r="I155" s="4" t="inlineStr">
         <is>
           <t>KSVEntgV § 1 und KSK-Info 10: nur die dort genannten nachgewiesenen Nebenleistungen fallen aus der Bemessung. Beleg erforderlich.</t>
         </is>
       </c>
-      <c r="J155" t="inlineStr">
+      <c r="J155" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="156">
-      <c r="A156" t="inlineStr">
+      <c r="A156" s="4" t="inlineStr">
         <is>
           <t>auslage.mit_beleg_ausgenommen</t>
         </is>
       </c>
-      <c r="B156" t="inlineStr">
+      <c r="B156" s="4" t="inlineStr">
         <is>
           <t>kostenübernahme</t>
         </is>
       </c>
-      <c r="C156" t="inlineStr">
+      <c r="C156" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E156" t="n">
+      <c r="E156" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H156" t="inlineStr">
+      <c r="H156" s="4" t="inlineStr">
         <is>
           <t>KSVEntgV-1</t>
         </is>
       </c>
-      <c r="I156" t="inlineStr">
+      <c r="I156" s="4" t="inlineStr">
         <is>
           <t>KSVEntgV § 1 und KSK-Info 10: nur die dort genannten nachgewiesenen Nebenleistungen fallen aus der Bemessung. Beleg erforderlich.</t>
         </is>
       </c>
-      <c r="J156" t="inlineStr">
+      <c r="J156" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="157">
-      <c r="A157" t="inlineStr">
+      <c r="A157" s="4" t="inlineStr">
         <is>
           <t>auslage.auch_ohne_beleg_ausgenommen</t>
         </is>
       </c>
-      <c r="B157" t="inlineStr">
+      <c r="B157" s="4" t="inlineStr">
         <is>
           <t>notenkauf</t>
         </is>
       </c>
-      <c r="C157" t="inlineStr">
+      <c r="C157" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E157" t="n">
+      <c r="E157" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H157" t="inlineStr">
+      <c r="H157" s="4" t="inlineStr">
         <is>
           <t>KSVEntgV-1</t>
         </is>
       </c>
-      <c r="I157" t="inlineStr">
+      <c r="I157" s="4" t="inlineStr">
         <is>
           <t>Weiterberechnete Auslage Noten oder Kostenübernahme, wie bisher im Register auslage.nachgewiesen geführt.</t>
         </is>
       </c>
-      <c r="J157" t="inlineStr">
+      <c r="J157" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="158">
-      <c r="A158" t="inlineStr">
+      <c r="A158" s="4" t="inlineStr">
         <is>
           <t>auslage.auch_ohne_beleg_ausgenommen</t>
         </is>
       </c>
-      <c r="B158" t="inlineStr">
+      <c r="B158" s="4" t="inlineStr">
         <is>
           <t>kostenübernahme</t>
         </is>
       </c>
-      <c r="C158" t="inlineStr">
+      <c r="C158" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E158" t="n">
+      <c r="E158" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H158" t="inlineStr">
+      <c r="H158" s="4" t="inlineStr">
         <is>
           <t>KSVEntgV-1</t>
         </is>
       </c>
-      <c r="I158" t="inlineStr">
+      <c r="I158" s="4" t="inlineStr">
         <is>
           <t>Weiterberechnete Auslage Noten oder Kostenübernahme, wie bisher im Register auslage.nachgewiesen geführt.</t>
         </is>
       </c>
-      <c r="J158" t="inlineStr">
+      <c r="J158" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="159">
-      <c r="A159" t="inlineStr">
+      <c r="A159" s="4" t="inlineStr">
         <is>
           <t>auslage.auch_ohne_beleg_ausgenommen</t>
         </is>
       </c>
-      <c r="B159" t="inlineStr">
+      <c r="B159" s="4" t="inlineStr">
         <is>
           <t>notenmappe</t>
         </is>
       </c>
-      <c r="C159" t="inlineStr">
+      <c r="C159" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E159" t="n">
+      <c r="E159" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H159" t="inlineStr">
+      <c r="H159" s="4" t="inlineStr">
         <is>
           <t>KSVEntgV-1</t>
         </is>
       </c>
-      <c r="I159" t="inlineStr">
+      <c r="I159" s="4" t="inlineStr">
         <is>
           <t>Weiterberechnete Auslage Noten oder Kostenübernahme, wie bisher im Register auslage.nachgewiesen geführt.</t>
         </is>
       </c>
-      <c r="J159" t="inlineStr">
+      <c r="J159" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="160">
-      <c r="A160" t="inlineStr">
+      <c r="A160" s="4" t="inlineStr">
         <is>
           <t>auslage.ohne_beleg_offen</t>
         </is>
       </c>
-      <c r="B160" t="inlineStr">
+      <c r="B160" s="4" t="inlineStr">
         <is>
           <t>auslage</t>
         </is>
       </c>
-      <c r="C160" t="inlineStr">
+      <c r="C160" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E160" t="n">
+      <c r="E160" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H160" t="inlineStr">
+      <c r="H160" s="4" t="inlineStr">
         <is>
           <t>KSVEntgV-1</t>
         </is>
       </c>
-      <c r="I160" t="inlineStr">
+      <c r="I160" s="4" t="inlineStr">
         <is>
           <t>KSVEntgV § 1 Nr. 1 und Info 10: ohne Nachweis keine Ausnahme. Verpflegung zusätzlich an verpflegung.stunden_grenze und verpflegung.stunden_ganztag im Register gebunden.</t>
         </is>
       </c>
-      <c r="J160" t="inlineStr">
+      <c r="J160" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="161">
-      <c r="A161" t="inlineStr">
+      <c r="A161" s="4" t="inlineStr">
         <is>
           <t>auslage.ohne_beleg_offen</t>
         </is>
       </c>
-      <c r="B161" t="inlineStr">
+      <c r="B161" s="4" t="inlineStr">
         <is>
           <t>materialkosten</t>
         </is>
       </c>
-      <c r="C161" t="inlineStr">
+      <c r="C161" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E161" t="n">
+      <c r="E161" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H161" t="inlineStr">
+      <c r="H161" s="4" t="inlineStr">
         <is>
           <t>KSVEntgV-1</t>
         </is>
       </c>
-      <c r="I161" t="inlineStr">
+      <c r="I161" s="4" t="inlineStr">
         <is>
           <t>KSVEntgV § 1 Nr. 1 und Info 10: ohne Nachweis keine Ausnahme. Verpflegung zusätzlich an verpflegung.stunden_grenze und verpflegung.stunden_ganztag im Register gebunden.</t>
         </is>
       </c>
-      <c r="J161" t="inlineStr">
+      <c r="J161" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="162">
-      <c r="A162" t="inlineStr">
+      <c r="A162" s="4" t="inlineStr">
         <is>
           <t>auslage.ohne_beleg_offen</t>
         </is>
       </c>
-      <c r="B162" t="inlineStr">
+      <c r="B162" s="4" t="inlineStr">
         <is>
           <t>reise</t>
         </is>
       </c>
-      <c r="C162" t="inlineStr">
+      <c r="C162" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E162" t="n">
+      <c r="E162" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H162" t="inlineStr">
+      <c r="H162" s="4" t="inlineStr">
         <is>
           <t>KSVEntgV-1</t>
         </is>
       </c>
-      <c r="I162" t="inlineStr">
+      <c r="I162" s="4" t="inlineStr">
         <is>
           <t>KSVEntgV § 1 Nr. 1 und Info 10: ohne Nachweis keine Ausnahme. Verpflegung zusätzlich an verpflegung.stunden_grenze und verpflegung.stunden_ganztag im Register gebunden.</t>
         </is>
       </c>
-      <c r="J162" t="inlineStr">
+      <c r="J162" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="163">
-      <c r="A163" t="inlineStr">
+      <c r="A163" s="4" t="inlineStr">
         <is>
           <t>auslage.ohne_beleg_offen</t>
         </is>
       </c>
-      <c r="B163" t="inlineStr">
+      <c r="B163" s="4" t="inlineStr">
         <is>
           <t>fahrt</t>
         </is>
       </c>
-      <c r="C163" t="inlineStr">
+      <c r="C163" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E163" t="n">
+      <c r="E163" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H163" t="inlineStr">
+      <c r="H163" s="4" t="inlineStr">
         <is>
           <t>KSVEntgV-1</t>
         </is>
       </c>
-      <c r="I163" t="inlineStr">
+      <c r="I163" s="4" t="inlineStr">
         <is>
           <t>KSVEntgV § 1 Nr. 1 und Info 10: ohne Nachweis keine Ausnahme. Verpflegung zusätzlich an verpflegung.stunden_grenze und verpflegung.stunden_ganztag im Register gebunden.</t>
         </is>
       </c>
-      <c r="J163" t="inlineStr">
+      <c r="J163" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="164">
-      <c r="A164" t="inlineStr">
+      <c r="A164" s="4" t="inlineStr">
         <is>
           <t>auslage.ohne_beleg_offen</t>
         </is>
       </c>
-      <c r="B164" t="inlineStr">
+      <c r="B164" s="4" t="inlineStr">
         <is>
           <t>hotel</t>
         </is>
       </c>
-      <c r="C164" t="inlineStr">
+      <c r="C164" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E164" t="n">
+      <c r="E164" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H164" t="inlineStr">
+      <c r="H164" s="4" t="inlineStr">
         <is>
           <t>KSVEntgV-1</t>
         </is>
       </c>
-      <c r="I164" t="inlineStr">
+      <c r="I164" s="4" t="inlineStr">
         <is>
           <t>KSVEntgV § 1 Nr. 1 und Info 10: ohne Nachweis keine Ausnahme. Verpflegung zusätzlich an verpflegung.stunden_grenze und verpflegung.stunden_ganztag im Register gebunden.</t>
         </is>
       </c>
-      <c r="J164" t="inlineStr">
+      <c r="J164" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="165">
-      <c r="A165" t="inlineStr">
+      <c r="A165" s="4" t="inlineStr">
         <is>
           <t>auslage.ohne_beleg_offen</t>
         </is>
       </c>
-      <c r="B165" t="inlineStr">
+      <c r="B165" s="4" t="inlineStr">
         <is>
           <t>übernachtung</t>
         </is>
       </c>
-      <c r="C165" t="inlineStr">
+      <c r="C165" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E165" t="n">
+      <c r="E165" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H165" t="inlineStr">
+      <c r="H165" s="4" t="inlineStr">
         <is>
           <t>KSVEntgV-1</t>
         </is>
       </c>
-      <c r="I165" t="inlineStr">
+      <c r="I165" s="4" t="inlineStr">
         <is>
           <t>KSVEntgV § 1 Nr. 1 und Info 10: ohne Nachweis keine Ausnahme. Verpflegung zusätzlich an verpflegung.stunden_grenze und verpflegung.stunden_ganztag im Register gebunden.</t>
         </is>
       </c>
-      <c r="J165" t="inlineStr">
+      <c r="J165" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="166">
-      <c r="A166" t="inlineStr">
+      <c r="A166" s="4" t="inlineStr">
         <is>
           <t>auslage.ohne_beleg_offen</t>
         </is>
       </c>
-      <c r="B166" t="inlineStr">
+      <c r="B166" s="4" t="inlineStr">
         <is>
           <t>uebernachtung</t>
         </is>
       </c>
-      <c r="C166" t="inlineStr">
+      <c r="C166" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E166" t="n">
+      <c r="E166" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H166" t="inlineStr">
+      <c r="H166" s="4" t="inlineStr">
         <is>
           <t>KSVEntgV-1</t>
         </is>
       </c>
-      <c r="I166" t="inlineStr">
+      <c r="I166" s="4" t="inlineStr">
         <is>
           <t>KSVEntgV § 1 Nr. 1 und Info 10: ohne Nachweis keine Ausnahme. Verpflegung zusätzlich an verpflegung.stunden_grenze und verpflegung.stunden_ganztag im Register gebunden.</t>
         </is>
       </c>
-      <c r="J166" t="inlineStr">
+      <c r="J166" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="167">
-      <c r="A167" t="inlineStr">
+      <c r="A167" s="4" t="inlineStr">
         <is>
           <t>auslage.ohne_beleg_offen</t>
         </is>
       </c>
-      <c r="B167" t="inlineStr">
+      <c r="B167" s="4" t="inlineStr">
         <is>
           <t>verpflegung</t>
         </is>
       </c>
-      <c r="C167" t="inlineStr">
+      <c r="C167" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E167" t="n">
+      <c r="E167" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H167" t="inlineStr">
+      <c r="H167" s="4" t="inlineStr">
         <is>
           <t>KSVEntgV-1</t>
         </is>
       </c>
-      <c r="I167" t="inlineStr">
+      <c r="I167" s="4" t="inlineStr">
         <is>
           <t>KSVEntgV § 1 Nr. 1 und Info 10: ohne Nachweis keine Ausnahme. Verpflegung zusätzlich an verpflegung.stunden_grenze und verpflegung.stunden_ganztag im Register gebunden.</t>
         </is>
       </c>
-      <c r="J167" t="inlineStr">
+      <c r="J167" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="168">
-      <c r="A168" t="inlineStr">
+      <c r="A168" s="4" t="inlineStr">
         <is>
           <t>auslage.gehoert_zum_entgelt</t>
         </is>
       </c>
-      <c r="B168" t="inlineStr">
+      <c r="B168" s="4" t="inlineStr">
         <is>
           <t>porto</t>
         </is>
       </c>
-      <c r="C168" t="inlineStr">
+      <c r="C168" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E168" t="n">
+      <c r="E168" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H168" t="inlineStr">
+      <c r="H168" s="4" t="inlineStr">
         <is>
           <t>Info-10</t>
         </is>
       </c>
-      <c r="I168" t="inlineStr">
+      <c r="I168" s="4" t="inlineStr">
         <is>
           <t>KSK-Info 10, S. 1: Auslagen und Nebenkosten, die dem Künstler vergütet werden, gehören zum Entgelt. Ausnahme nur Umsatzsteuer, Verwertungsgesellschaft, Reise und übliche Bewirtung.</t>
         </is>
       </c>
-      <c r="J168" t="inlineStr">
+      <c r="J168" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="169">
-      <c r="A169" t="inlineStr">
+      <c r="A169" s="4" t="inlineStr">
         <is>
           <t>auslage.gehoert_zum_entgelt</t>
         </is>
       </c>
-      <c r="B169" t="inlineStr">
+      <c r="B169" s="4" t="inlineStr">
         <is>
           <t>versand</t>
         </is>
       </c>
-      <c r="C169" t="inlineStr">
+      <c r="C169" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E169" t="n">
+      <c r="E169" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H169" t="inlineStr">
+      <c r="H169" s="4" t="inlineStr">
         <is>
           <t>Info-10</t>
         </is>
       </c>
-      <c r="I169" t="inlineStr">
+      <c r="I169" s="4" t="inlineStr">
         <is>
           <t>KSK-Info 10, S. 1: Auslagen und Nebenkosten, die dem Künstler vergütet werden, gehören zum Entgelt. Ausnahme nur Umsatzsteuer, Verwertungsgesellschaft, Reise und übliche Bewirtung.</t>
         </is>
       </c>
-      <c r="J169" t="inlineStr">
+      <c r="J169" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="170">
-      <c r="A170" t="inlineStr">
+      <c r="A170" s="4" t="inlineStr">
         <is>
           <t>auslage.gehoert_zum_entgelt</t>
         </is>
       </c>
-      <c r="B170" t="inlineStr">
+      <c r="B170" s="4" t="inlineStr">
         <is>
           <t>kopierkosten</t>
         </is>
       </c>
-      <c r="C170" t="inlineStr">
+      <c r="C170" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E170" t="n">
+      <c r="E170" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H170" t="inlineStr">
+      <c r="H170" s="4" t="inlineStr">
         <is>
           <t>Info-10</t>
         </is>
       </c>
-      <c r="I170" t="inlineStr">
+      <c r="I170" s="4" t="inlineStr">
         <is>
           <t>KSK-Info 10, S. 1: Auslagen und Nebenkosten, die dem Künstler vergütet werden, gehören zum Entgelt. Ausnahme nur Umsatzsteuer, Verwertungsgesellschaft, Reise und übliche Bewirtung.</t>
         </is>
       </c>
-      <c r="J170" t="inlineStr">
+      <c r="J170" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="171">
-      <c r="A171" t="inlineStr">
+      <c r="A171" s="4" t="inlineStr">
         <is>
           <t>auslage.gehoert_zum_entgelt</t>
         </is>
       </c>
-      <c r="B171" t="inlineStr">
+      <c r="B171" s="4" t="inlineStr">
         <is>
           <t>rahmen</t>
         </is>
       </c>
-      <c r="C171" t="inlineStr">
+      <c r="C171" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E171" t="n">
+      <c r="E171" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H171" t="inlineStr">
+      <c r="H171" s="4" t="inlineStr">
         <is>
           <t>Info-10</t>
         </is>
       </c>
-      <c r="I171" t="inlineStr">
+      <c r="I171" s="4" t="inlineStr">
         <is>
           <t>KSK-Info 10, S. 1: Auslagen und Nebenkosten, die dem Künstler vergütet werden, gehören zum Entgelt. Ausnahme nur Umsatzsteuer, Verwertungsgesellschaft, Reise und übliche Bewirtung.</t>
         </is>
       </c>
-      <c r="J171" t="inlineStr">
+      <c r="J171" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="172">
-      <c r="A172" t="inlineStr">
+      <c r="A172" s="4" t="inlineStr">
         <is>
           <t>auslage.gehoert_zum_entgelt</t>
         </is>
       </c>
-      <c r="B172" t="inlineStr">
+      <c r="B172" s="4" t="inlineStr">
         <is>
           <t>plakat</t>
         </is>
       </c>
-      <c r="C172" t="inlineStr">
+      <c r="C172" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E172" t="n">
+      <c r="E172" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H172" t="inlineStr">
+      <c r="H172" s="4" t="inlineStr">
         <is>
           <t>Info-10</t>
         </is>
       </c>
-      <c r="I172" t="inlineStr">
+      <c r="I172" s="4" t="inlineStr">
         <is>
           <t>KSK-Info 10, S. 1: Auslagen und Nebenkosten, die dem Künstler vergütet werden, gehören zum Entgelt. Ausnahme nur Umsatzsteuer, Verwertungsgesellschaft, Reise und übliche Bewirtung.</t>
         </is>
       </c>
-      <c r="J172" t="inlineStr">
+      <c r="J172" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="173">
-      <c r="A173" t="inlineStr">
+      <c r="A173" s="4" t="inlineStr">
         <is>
           <t>auslage.gehoert_zum_entgelt</t>
         </is>
       </c>
-      <c r="B173" t="inlineStr">
+      <c r="B173" s="4" t="inlineStr">
         <is>
           <t>scanner-miete</t>
         </is>
       </c>
-      <c r="C173" t="inlineStr">
+      <c r="C173" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E173" t="n">
+      <c r="E173" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H173" t="inlineStr">
+      <c r="H173" s="4" t="inlineStr">
         <is>
           <t>Info-10</t>
         </is>
       </c>
-      <c r="I173" t="inlineStr">
+      <c r="I173" s="4" t="inlineStr">
         <is>
           <t>KSK-Info 10, S. 1: Auslagen und Nebenkosten, die dem Künstler vergütet werden, gehören zum Entgelt. Ausnahme nur Umsatzsteuer, Verwertungsgesellschaft, Reise und übliche Bewirtung.</t>
         </is>
       </c>
-      <c r="J173" t="inlineStr">
+      <c r="J173" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="174">
-      <c r="A174" t="inlineStr">
+      <c r="A174" s="4" t="inlineStr">
         <is>
           <t>auslage.gehoert_zum_entgelt</t>
         </is>
       </c>
-      <c r="B174" t="inlineStr">
+      <c r="B174" s="4" t="inlineStr">
         <is>
           <t>notenmaterial</t>
         </is>
       </c>
-      <c r="C174" t="inlineStr">
+      <c r="C174" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E174" t="n">
+      <c r="E174" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H174" t="inlineStr">
+      <c r="H174" s="4" t="inlineStr">
         <is>
           <t>Info-10</t>
         </is>
       </c>
-      <c r="I174" t="inlineStr">
+      <c r="I174" s="4" t="inlineStr">
         <is>
           <t>KSK-Info 10, S. 1: Auslagen und Nebenkosten, die dem Künstler vergütet werden, gehören zum Entgelt. Ausnahme nur Umsatzsteuer, Verwertungsgesellschaft, Reise und übliche Bewirtung.</t>
         </is>
       </c>
-      <c r="J174" t="inlineStr">
+      <c r="J174" s="4" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>offen.waehrung</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Fremdwährung ohne Umrechnungsnachweis — Kurs und Nachweis vorlegen</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E175" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>Testfall L-23: Euro-Betrag und Umrechnungsgrundlage klären; keine erfundene Euro-Summe. Eine Umrechnungsregel ist in der Quellenbasis nicht belegt.</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>auslage.mit_beleg_ausgenommen</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>verpflegungsmehraufwand</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E176" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>KSVEntgV-1</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>KSVEntgV § 1 Nr. 1: nachgewiesene Reisekosten innerhalb der Grenzen des § 3 Nr. 16 EStG zählen nicht. KSK-Info 10, S. 2.</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>auslage.gehoert_zum_entgelt</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>plakatrahmen</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E177" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Info-10</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>KSK-Info 10, S. 1: Auslagen und Nebenkosten, die dem Künstler vergütet werden, gehören zum Entgelt. Ausnahme nur Umsatzsteuer, Verwertungsgesellschaft, Reise und übliche Bewirtung.</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>

--- a/regelwerk/Regelkatalog_24_KSVG_Entwurf.xlsx
+++ b/regelwerk/Regelkatalog_24_KSVG_Entwurf.xlsx
@@ -15138,7 +15138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J177"/>
+  <dimension ref="A1:J178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" style="5" min="1" max="1"/>
@@ -21471,105 +21471,140 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" t="inlineStr">
+      <c r="A175" s="4" t="inlineStr">
         <is>
           <t>offen.waehrung</t>
         </is>
       </c>
-      <c r="B175" t="inlineStr">
+      <c r="B175" s="4" t="inlineStr">
         <is>
           <t>Fremdwährung ohne Umrechnungsnachweis — Kurs und Nachweis vorlegen</t>
         </is>
       </c>
-      <c r="C175" t="inlineStr">
+      <c r="C175" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E175" t="n">
+      <c r="E175" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H175" t="inlineStr">
+      <c r="H175" s="4" t="inlineStr">
         <is>
           <t>A3</t>
         </is>
       </c>
-      <c r="I175" t="inlineStr">
+      <c r="I175" s="4" t="inlineStr">
         <is>
           <t>Testfall L-23: Euro-Betrag und Umrechnungsgrundlage klären; keine erfundene Euro-Summe. Eine Umrechnungsregel ist in der Quellenbasis nicht belegt.</t>
         </is>
       </c>
-      <c r="J175" t="inlineStr">
+      <c r="J175" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="176">
-      <c r="A176" t="inlineStr">
+      <c r="A176" s="4" t="inlineStr">
         <is>
           <t>auslage.mit_beleg_ausgenommen</t>
         </is>
       </c>
-      <c r="B176" t="inlineStr">
+      <c r="B176" s="4" t="inlineStr">
         <is>
           <t>verpflegungsmehraufwand</t>
         </is>
       </c>
-      <c r="C176" t="inlineStr">
+      <c r="C176" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E176" t="n">
+      <c r="E176" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H176" t="inlineStr">
+      <c r="H176" s="4" t="inlineStr">
         <is>
           <t>KSVEntgV-1</t>
         </is>
       </c>
-      <c r="I176" t="inlineStr">
+      <c r="I176" s="4" t="inlineStr">
         <is>
           <t>KSVEntgV § 1 Nr. 1: nachgewiesene Reisekosten innerhalb der Grenzen des § 3 Nr. 16 EStG zählen nicht. KSK-Info 10, S. 2.</t>
         </is>
       </c>
-      <c r="J176" t="inlineStr">
+      <c r="J176" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
       </c>
     </row>
     <row r="177">
-      <c r="A177" t="inlineStr">
+      <c r="A177" s="4" t="inlineStr">
         <is>
           <t>auslage.gehoert_zum_entgelt</t>
         </is>
       </c>
-      <c r="B177" t="inlineStr">
+      <c r="B177" s="4" t="inlineStr">
         <is>
           <t>plakatrahmen</t>
         </is>
       </c>
-      <c r="C177" t="inlineStr">
+      <c r="C177" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E177" t="n">
+      <c r="E177" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H177" t="inlineStr">
+      <c r="H177" s="4" t="inlineStr">
         <is>
           <t>Info-10</t>
         </is>
       </c>
-      <c r="I177" t="inlineStr">
+      <c r="I177" s="4" t="inlineStr">
         <is>
           <t>KSK-Info 10, S. 1: Auslagen und Nebenkosten, die dem Künstler vergütet werden, gehören zum Entgelt. Ausnahme nur Umsatzsteuer, Verwertungsgesellschaft, Reise und übliche Bewirtung.</t>
         </is>
       </c>
-      <c r="J177" t="inlineStr">
+      <c r="J177" s="4" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>sperre.rechtsform</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Widerspruch der Rechtsform: mehrere Gesellschaftsformen im selben Dokument</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E178" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>Rechenprobe A2/A3: widerspruechliche Angaben zur Rechtsform, keine stille Wahl</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>

--- a/regelwerk/Regelkatalog_24_KSVG_Entwurf.xlsx
+++ b/regelwerk/Regelkatalog_24_KSVG_Entwurf.xlsx
@@ -15138,7 +15138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J178"/>
+  <dimension ref="A1:J182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" style="5" min="1" max="1"/>
@@ -21576,35 +21576,175 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" t="inlineStr">
+      <c r="A178" s="4" t="inlineStr">
         <is>
           <t>sperre.rechtsform</t>
         </is>
       </c>
-      <c r="B178" t="inlineStr">
+      <c r="B178" s="4" t="inlineStr">
         <is>
           <t>Widerspruch der Rechtsform: mehrere Gesellschaftsformen im selben Dokument</t>
         </is>
       </c>
-      <c r="C178" t="inlineStr">
+      <c r="C178" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="E178" t="n">
+      <c r="E178" s="4" t="n">
         <v>2015</v>
       </c>
-      <c r="H178" t="inlineStr">
+      <c r="H178" s="4" t="inlineStr">
         <is>
           <t>A2</t>
         </is>
       </c>
-      <c r="I178" t="inlineStr">
+      <c r="I178" s="4" t="inlineStr">
         <is>
           <t>Rechenprobe A2/A3: widerspruechliche Angaben zur Rechtsform, keine stille Wahl</t>
         </is>
       </c>
-      <c r="J178" t="inlineStr">
+      <c r="J178" s="4" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="4" t="inlineStr">
+        <is>
+          <t>ust.satz</t>
+        </is>
+      </c>
+      <c r="B179" s="4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C179" s="4" t="inlineStr">
+        <is>
+          <t>Prozent</t>
+        </is>
+      </c>
+      <c r="E179" s="4" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H179" s="4" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="I179" s="4" t="inlineStr">
+        <is>
+          <t>UStG § 12 Abs. 2: ermäßigter Steuersatz 7 Prozent. Der Satz steht im Register, nicht im Code.</t>
+        </is>
+      </c>
+      <c r="J179" s="4" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="4" t="inlineStr">
+        <is>
+          <t>ust.satz</t>
+        </is>
+      </c>
+      <c r="B180" s="4" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C180" s="4" t="inlineStr">
+        <is>
+          <t>Prozent</t>
+        </is>
+      </c>
+      <c r="E180" s="4" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H180" s="4" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="I180" s="4" t="inlineStr">
+        <is>
+          <t>UStG § 12 Abs. 1: Regelsteuersatz 19 Prozent. Der Satz steht im Register, nicht im Code.</t>
+        </is>
+      </c>
+      <c r="J180" s="4" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="4" t="inlineStr">
+        <is>
+          <t>sperre.ust_mischsatz</t>
+        </is>
+      </c>
+      <c r="B181" s="4" t="inlineStr">
+        <is>
+          <t>USt-Rechenprobe, Mischsaetze</t>
+        </is>
+      </c>
+      <c r="C181" s="4" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E181" s="4" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H181" s="4" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="I181" s="4" t="inlineStr">
+        <is>
+          <t>§ 25 Abs. 1 KSVG: die Abgabe bemisst sich nach dem Entgelt. Rechenprobe: ausgewiesene Umsatzsteuer passt zu keinem Satz und die Summe zu keinem einheitlichen Satz.</t>
+        </is>
+      </c>
+      <c r="J181" s="4" t="inlineStr">
+        <is>
+          <t>Entwurf – vom Steuerberater zu prüfen</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="4" t="inlineStr">
+        <is>
+          <t>offen.oeffentliche_stelle</t>
+        </is>
+      </c>
+      <c r="B182" s="4" t="inlineStr">
+        <is>
+          <t>Öffentliche Stelle als Verwerter: Info 11/16, Rückfrage ob die Verwertereigenschaft in Betracht kommt.</t>
+        </is>
+      </c>
+      <c r="C182" s="4" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E182" s="4" t="n">
+        <v>2015</v>
+      </c>
+      <c r="H182" s="4" t="inlineStr">
+        <is>
+          <t>Info-11</t>
+        </is>
+      </c>
+      <c r="I182" s="4" t="inlineStr">
+        <is>
+          <t>KSK-Info 11, S. 1 Abschn. 1-2: Städte, Landkreise und Gemeinden können abgabepflichtig sein. KSK-Info 16, Stand 09.2025: Abgabepflicht öffentlich-rechtlicher Institutionen. Keine stille Ausnahme wie eine Zahlung an eine Kapitalgesellschaft.</t>
+        </is>
+      </c>
+      <c r="J182" s="4" t="inlineStr">
         <is>
           <t>Entwurf – vom Steuerberater zu prüfen</t>
         </is>
